--- a/docs/Mobile_App_Error_Alert_Messages.xlsx
+++ b/docs/Mobile_App_Error_Alert_Messages.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Messages'!$A$5:$J$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Messages'!$A$5:$H$412</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Messages'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J412"/>
+  <dimension ref="A1:H412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,9 +530,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -597,16 +595,6 @@
           <t>New Message (fill in)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Source (file:line)</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Code trigger (for developer)</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -647,16 +635,6 @@
       <c r="H6" s="5" t="inlineStr">
         <is>
           <t>No photos left on your plan. Delete one or upgrade your plan.</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:325</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Example only — shows how to fill column H</t>
         </is>
       </c>
     </row>
@@ -695,16 +673,6 @@
         </is>
       </c>
       <c r="H7" s="8" t="n"/>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_details_screen.dart:77</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>_moveDay()  if days.length &lt; 2</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -741,16 +709,6 @@
         </is>
       </c>
       <c r="H8" s="8" t="n"/>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_details_screen.dart:244</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -787,16 +745,6 @@
         </is>
       </c>
       <c r="H9" s="8" t="n"/>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_details_screen.dart:548</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>_confirmBody()</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -833,16 +781,6 @@
         </is>
       </c>
       <c r="H10" s="8" t="n"/>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_details_screen.dart:550</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>_confirmBody()</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -879,16 +817,6 @@
         </is>
       </c>
       <c r="H11" s="8" t="n"/>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_form_screen.dart:152</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>_addImage()  if _images.length &gt;= _maxImages</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -925,16 +853,6 @@
         </is>
       </c>
       <c r="H12" s="8" t="n"/>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_form_screen.dart:256</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>_saveOnce()</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -971,16 +889,6 @@
         </is>
       </c>
       <c r="H13" s="8" t="n"/>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_form_screen.dart:260</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>_saveOnce()  if _multiDay &amp;&amp; !_endDate!.isAfter(_date!)</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -1017,16 +925,6 @@
         </is>
       </c>
       <c r="H14" s="8" t="n"/>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_form_screen.dart:266</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>_saveOnce()  if !_multiDay &amp;&amp; _start == _end</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -1063,16 +961,6 @@
         </is>
       </c>
       <c r="H15" s="8" t="n"/>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_form_screen.dart:492</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>_counter()  if error</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -1109,16 +997,6 @@
         </is>
       </c>
       <c r="H16" s="8" t="n"/>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_list_screen.dart:139</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -1155,16 +1033,6 @@
         </is>
       </c>
       <c r="H17" s="8" t="n"/>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_widgets.dart:260</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -1201,16 +1069,6 @@
         </is>
       </c>
       <c r="H18" s="8" t="n"/>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/agenda/agenda_widgets.dart:262</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -1247,16 +1105,6 @@
         </is>
       </c>
       <c r="H19" s="8" t="n"/>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>features/common/auth/login_mobile_screen.dart:68</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>_sendOtp()  if !_agreed</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -1293,16 +1141,6 @@
         </is>
       </c>
       <c r="H20" s="8" t="n"/>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>features/common/auth/login_mobile_screen.dart:95</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>_sendOtp()  if challenge.devCode != null</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -1339,16 +1177,6 @@
         </is>
       </c>
       <c r="H21" s="8" t="n"/>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>features/common/auth/login_mobile_screen.dart:100</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>_sendOtp()  if !challenge.delivered</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -1385,16 +1213,6 @@
         </is>
       </c>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>features/common/auth/login_mobile_screen.dart:121</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>_verify()  if _code.length &lt; 6</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -1431,16 +1249,6 @@
         </is>
       </c>
       <c r="H23" s="8" t="n"/>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>features/common/auth/login_mobile_screen.dart:157</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>_verify()  if !mounted</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -1477,16 +1285,6 @@
         </is>
       </c>
       <c r="H24" s="8" t="n"/>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>features/common/auth/login_screen.dart:71</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -1523,16 +1321,6 @@
         </is>
       </c>
       <c r="H25" s="8" t="n"/>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/contact/organizer_contact_screens.dart:144</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>_launch()  if !ok &amp;&amp; context.mounted</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -1569,16 +1357,6 @@
         </is>
       </c>
       <c r="H26" s="8" t="n"/>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/contact/organizer_contact_screens.dart:148</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>_launch()  if context.mounted</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -1615,16 +1393,6 @@
         </is>
       </c>
       <c r="H27" s="8" t="n"/>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/contact/organizer_contact_screens.dart:158</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>_openCall()  if digits.isNotEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -1661,16 +1429,6 @@
         </is>
       </c>
       <c r="H28" s="8" t="n"/>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/contact/organizer_contact_screens.dart:167</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>_openWhatsApp()  if digits.isNotEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -1707,16 +1465,6 @@
         </is>
       </c>
       <c r="H29" s="8" t="n"/>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/contact/organizer_contact_screens.dart:177</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>_openMessage()  if digits.isNotEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -1753,16 +1501,6 @@
         </is>
       </c>
       <c r="H30" s="8" t="n"/>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/contact/organizer_contact_screens.dart:192</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>_openEmail()</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -1799,16 +1537,6 @@
         </is>
       </c>
       <c r="H31" s="8" t="n"/>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/contact/organizer_contact_screens.dart:975</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -1845,16 +1573,6 @@
         </is>
       </c>
       <c r="H32" s="8" t="n"/>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/contact/organizer_contact_screens.dart:1013</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1891,16 +1609,6 @@
         </is>
       </c>
       <c r="H33" s="8" t="n"/>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/contact/organizer_contact_screens.dart:1046</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>build()  if email.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -1937,16 +1645,6 @@
         </is>
       </c>
       <c r="H34" s="8" t="n"/>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/contact/organizer_contact_screens.dart:1165</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>build()  if digits.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -1983,16 +1681,6 @@
         </is>
       </c>
       <c r="H35" s="8" t="n"/>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>core/network/api_exception.dart:71</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>if res == null</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -2029,12 +1717,6 @@
         </is>
       </c>
       <c r="H36" s="8" t="n"/>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>core/network/api_exception.dart:73</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -2071,12 +1753,6 @@
         </is>
       </c>
       <c r="H37" s="8" t="n"/>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>core/network/api_exception.dart:75</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -2113,16 +1789,6 @@
         </is>
       </c>
       <c r="H38" s="8" t="n"/>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>core/network/api_exception.dart:124</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>_fallbackFor()</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -2159,16 +1825,6 @@
         </is>
       </c>
       <c r="H39" s="8" t="n"/>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>core/network/api_exception.dart:125</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>_fallbackFor()</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -2205,16 +1861,6 @@
         </is>
       </c>
       <c r="H40" s="8" t="n"/>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>core/network/api_exception.dart:127</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>_fallbackFor()</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -2251,16 +1897,6 @@
         </is>
       </c>
       <c r="H41" s="8" t="n"/>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>core/network/api_exception.dart:128</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>_fallbackFor()</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -2297,16 +1933,6 @@
         </is>
       </c>
       <c r="H42" s="8" t="n"/>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>core/network/api_exception.dart:129</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr">
-        <is>
-          <t>_fallbackFor()</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -2343,16 +1969,6 @@
         </is>
       </c>
       <c r="H43" s="8" t="n"/>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>core/network/api_exception.dart:130</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>_fallbackFor()</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -2389,16 +2005,6 @@
         </is>
       </c>
       <c r="H44" s="8" t="n"/>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>core/network/api_exception.dart:131</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>_fallbackFor()</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -2435,16 +2041,6 @@
         </is>
       </c>
       <c r="H45" s="8" t="n"/>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:90</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>byName()</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -2481,16 +2077,6 @@
         </is>
       </c>
       <c r="H46" s="8" t="n"/>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:516</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>_selectTemplate()</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -2527,16 +2113,6 @@
         </is>
       </c>
       <c r="H47" s="8" t="n"/>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:527</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>_selectTemplate()  if !RegExp(r'^[^@\s]+@[^@\s]+\.[^@\s]+$').hasMatch(_email.text.trim())</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -2573,16 +2149,6 @@
         </is>
       </c>
       <c r="H48" s="8" t="n"/>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:535</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>_selectTemplate()  if _name.text.trim().isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -2619,16 +2185,6 @@
         </is>
       </c>
       <c r="H49" s="8" t="n"/>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:551</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>_selectTemplate()</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -2665,16 +2221,6 @@
         </is>
       </c>
       <c r="H50" s="8" t="n"/>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:554</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>_selectTemplate()</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -2711,16 +2257,6 @@
         </is>
       </c>
       <c r="H51" s="8" t="n"/>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:561</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>_problem()  if case 0</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -2757,16 +2293,6 @@
         </is>
       </c>
       <c r="H52" s="8" t="n"/>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:593</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="inlineStr">
-        <is>
-          <t>_confirmDates()  if _datesConfirmed == key</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -2803,16 +2329,6 @@
         </is>
       </c>
       <c r="H53" s="8" t="n"/>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:594</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>_confirmDates()  if _datesConfirmed == key</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -2849,16 +2365,6 @@
         </is>
       </c>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:666</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>_nextDesignPage()</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -2895,16 +2401,6 @@
         </is>
       </c>
       <c r="H55" s="8" t="n"/>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:673</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>_nextDesignPage()</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -2941,16 +2437,6 @@
         </is>
       </c>
       <c r="H56" s="8" t="n"/>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:1038</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr">
-        <is>
-          <t>say()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -2987,16 +2473,6 @@
         </is>
       </c>
       <c r="H57" s="8" t="n"/>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:1052</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>_searchPlace()  if found.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -3033,16 +2509,6 @@
         </is>
       </c>
       <c r="H58" s="8" t="n"/>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:1060</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="inlineStr">
-        <is>
-          <t>_searchPlace()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -3079,16 +2545,6 @@
         </is>
       </c>
       <c r="H59" s="8" t="n"/>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:1154</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>_pickDate()  if _dateLocked</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -3125,16 +2581,6 @@
         </is>
       </c>
       <c r="H60" s="8" t="n"/>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:1211</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -3171,16 +2617,6 @@
         </is>
       </c>
       <c r="H61" s="8" t="n"/>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:1275</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>_sectionScaffold()</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -3217,16 +2653,6 @@
         </is>
       </c>
       <c r="H62" s="8" t="n"/>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:1515</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>_privacySection()</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -3263,16 +2689,6 @@
         </is>
       </c>
       <c r="H63" s="8" t="n"/>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:1646</t>
-        </is>
-      </c>
-      <c r="J63" s="7" t="inlineStr">
-        <is>
-          <t>_downloadQr()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -3309,16 +2725,6 @@
         </is>
       </c>
       <c r="H64" s="8" t="n"/>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:1659</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="inlineStr">
-        <is>
-          <t>_downloadQr()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -3355,16 +2761,6 @@
         </is>
       </c>
       <c r="H65" s="8" t="n"/>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:2556</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>_pickCustomColor()</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -3401,16 +2797,6 @@
         </is>
       </c>
       <c r="H66" s="8" t="n"/>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:2590</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="inlineStr">
-        <is>
-          <t>_pickCustomSecondaryColor()</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -3447,16 +2833,6 @@
         </is>
       </c>
       <c r="H67" s="8" t="n"/>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/create/create_event_screen.dart:2668</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="inlineStr">
-        <is>
-          <t>_menusStep()  if menus[i].isDefault</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -3493,16 +2869,6 @@
         </is>
       </c>
       <c r="H68" s="8" t="n"/>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>features/common/dev/component_gallery_screen.dart:281</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="inlineStr">
-        <is>
-          <t>_showConfirm()</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -3539,16 +2905,6 @@
         </is>
       </c>
       <c r="H69" s="8" t="n"/>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>features/common/dev/component_gallery_screen.dart:282</t>
-        </is>
-      </c>
-      <c r="J69" s="7" t="inlineStr">
-        <is>
-          <t>_showConfirm()</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -3585,16 +2941,6 @@
         </is>
       </c>
       <c r="H70" s="8" t="n"/>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>features/common/dev/component_gallery_screen.dart:284</t>
-        </is>
-      </c>
-      <c r="J70" s="7" t="inlineStr">
-        <is>
-          <t>_showConfirm()</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -3631,16 +2977,6 @@
         </is>
       </c>
       <c r="H71" s="8" t="n"/>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>features/common/dev/component_gallery_screen.dart:299</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr">
-        <is>
-          <t>_showStatus()</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -3677,16 +3013,6 @@
         </is>
       </c>
       <c r="H72" s="8" t="n"/>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>features/common/dev/component_gallery_screen.dart:300</t>
-        </is>
-      </c>
-      <c r="J72" s="7" t="inlineStr">
-        <is>
-          <t>_showStatus()</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -3723,16 +3049,6 @@
         </is>
       </c>
       <c r="H73" s="8" t="n"/>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/edit/edit_event_screen.dart:118</t>
-        </is>
-      </c>
-      <c r="J73" s="7" t="inlineStr">
-        <is>
-          <t>_publish()</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -3769,16 +3085,6 @@
         </is>
       </c>
       <c r="H74" s="8" t="n"/>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/edit/edit_event_screen.dart:119</t>
-        </is>
-      </c>
-      <c r="J74" s="7" t="inlineStr">
-        <is>
-          <t>_publish()</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -3815,16 +3121,6 @@
         </is>
       </c>
       <c r="H75" s="8" t="n"/>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/edit/event_settings_screen.dart:26</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr">
-        <is>
-          <t>soon()</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -3861,16 +3157,6 @@
         </is>
       </c>
       <c r="H76" s="8" t="n"/>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/edit/event_settings_screen.dart:50</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="inlineStr">
-        <is>
-          <t>soon()</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
@@ -3907,16 +3193,6 @@
         </is>
       </c>
       <c r="H77" s="8" t="n"/>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/edit/event_settings_screen.dart:167</t>
-        </is>
-      </c>
-      <c r="J77" s="7" t="inlineStr">
-        <is>
-          <t>_deleteOrArchive()  if choice == 'archive'</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -3953,16 +3229,6 @@
         </is>
       </c>
       <c r="H78" s="8" t="n"/>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/edit/event_settings_screen.dart:176</t>
-        </is>
-      </c>
-      <c r="J78" s="7" t="inlineStr">
-        <is>
-          <t>_deleteOrArchive()  if choice == 'archive'</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
@@ -3999,16 +3265,6 @@
         </is>
       </c>
       <c r="H79" s="8" t="n"/>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/edit/home_menu_settings_screen.dart:82</t>
-        </is>
-      </c>
-      <c r="J79" s="7" t="inlineStr">
-        <is>
-          <t>_load()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
@@ -4045,16 +3301,6 @@
         </is>
       </c>
       <c r="H80" s="8" t="n"/>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:113</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>_openActions()  if case _EventAction.viewAsParticipant</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -4091,16 +3337,6 @@
         </is>
       </c>
       <c r="H81" s="8" t="n"/>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:115</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="inlineStr">
-        <is>
-          <t>_openActions()  if case _EventAction.archive</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -4137,16 +3373,6 @@
         </is>
       </c>
       <c r="H82" s="8" t="n"/>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:119</t>
-        </is>
-      </c>
-      <c r="J82" s="7" t="inlineStr">
-        <is>
-          <t>_openActions()  if case _EventAction.duplicate</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -4183,16 +3409,6 @@
         </is>
       </c>
       <c r="H83" s="8" t="n"/>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:120</t>
-        </is>
-      </c>
-      <c r="J83" s="7" t="inlineStr">
-        <is>
-          <t>_openActions()  if case _EventAction.duplicate</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -4229,16 +3445,6 @@
         </is>
       </c>
       <c r="H84" s="8" t="n"/>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:144</t>
-        </is>
-      </c>
-      <c r="J84" s="7" t="inlineStr">
-        <is>
-          <t>_openActions()  if case _EventAction.delete</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -4275,16 +3481,6 @@
         </is>
       </c>
       <c r="H85" s="8" t="n"/>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:193</t>
-        </is>
-      </c>
-      <c r="J85" s="7" t="inlineStr">
-        <is>
-          <t>build()  if selectedId == null</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -4321,16 +3517,6 @@
         </is>
       </c>
       <c r="H86" s="8" t="n"/>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:210</t>
-        </is>
-      </c>
-      <c r="J86" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -4367,16 +3553,6 @@
         </is>
       </c>
       <c r="H87" s="8" t="n"/>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:210</t>
-        </is>
-      </c>
-      <c r="J87" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
@@ -4413,16 +3589,6 @@
         </is>
       </c>
       <c r="H88" s="8" t="n"/>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:212</t>
-        </is>
-      </c>
-      <c r="J88" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
@@ -4459,16 +3625,6 @@
         </is>
       </c>
       <c r="H89" s="8" t="n"/>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:216</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -4505,16 +3661,6 @@
         </is>
       </c>
       <c r="H90" s="8" t="n"/>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:227</t>
-        </is>
-      </c>
-      <c r="J90" s="7" t="inlineStr">
-        <is>
-          <t>build()  if event == null</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -4551,16 +3697,6 @@
         </is>
       </c>
       <c r="H91" s="8" t="n"/>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:228</t>
-        </is>
-      </c>
-      <c r="J91" s="7" t="inlineStr">
-        <is>
-          <t>build()  if event == null</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -4597,16 +3733,6 @@
         </is>
       </c>
       <c r="H92" s="8" t="n"/>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:563</t>
-        </is>
-      </c>
-      <c r="J92" s="7" t="inlineStr">
-        <is>
-          <t>_partialNote()</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -4643,16 +3769,6 @@
         </is>
       </c>
       <c r="H93" s="8" t="n"/>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/event/organizer_event_screen.dart:782</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="inlineStr">
-        <is>
-          <t>isDefault()  if route != null</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -4689,16 +3805,6 @@
         </is>
       </c>
       <c r="H94" s="8" t="n"/>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/event/participant_event_screen.dart:129</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>build()  if selectedId == null</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -4735,16 +3841,6 @@
         </is>
       </c>
       <c r="H95" s="8" t="n"/>
-      <c r="I95" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/event/participant_event_screen.dart:146</t>
-        </is>
-      </c>
-      <c r="J95" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -4781,16 +3877,6 @@
         </is>
       </c>
       <c r="H96" s="8" t="n"/>
-      <c r="I96" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/event/participant_event_screen.dart:146</t>
-        </is>
-      </c>
-      <c r="J96" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -4827,16 +3913,6 @@
         </is>
       </c>
       <c r="H97" s="8" t="n"/>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/event/participant_event_screen.dart:148</t>
-        </is>
-      </c>
-      <c r="J97" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -4873,16 +3949,6 @@
         </is>
       </c>
       <c r="H98" s="8" t="n"/>
-      <c r="I98" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/event/participant_event_screen.dart:152</t>
-        </is>
-      </c>
-      <c r="J98" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -4919,16 +3985,6 @@
         </is>
       </c>
       <c r="H99" s="8" t="n"/>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/event/participant_event_screen.dart:163</t>
-        </is>
-      </c>
-      <c r="J99" s="7" t="inlineStr">
-        <is>
-          <t>build()  if event == null</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -4965,16 +4021,6 @@
         </is>
       </c>
       <c r="H100" s="8" t="n"/>
-      <c r="I100" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/event/participant_event_screen.dart:164</t>
-        </is>
-      </c>
-      <c r="J100" s="7" t="inlineStr">
-        <is>
-          <t>build()  if event == null</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -5011,16 +4057,6 @@
         </is>
       </c>
       <c r="H101" s="8" t="n"/>
-      <c r="I101" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/event/participant_event_screen.dart:247</t>
-        </is>
-      </c>
-      <c r="J101" s="7" t="inlineStr">
-        <is>
-          <t>_partialNote()</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
@@ -5057,16 +4093,6 @@
         </is>
       </c>
       <c r="H102" s="8" t="n"/>
-      <c r="I102" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/event/participant_event_screen.dart:664</t>
-        </is>
-      </c>
-      <c r="J102" s="7" t="inlineStr">
-        <is>
-          <t>_exploreGrid()  if route != null</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
@@ -5103,16 +4129,6 @@
         </is>
       </c>
       <c r="H103" s="8" t="n"/>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/event_agenda_screen.dart:107</t>
-        </is>
-      </c>
-      <c r="J103" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
@@ -5149,16 +4165,6 @@
         </is>
       </c>
       <c r="H104" s="8" t="n"/>
-      <c r="I104" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/event_contact_screen.dart:43</t>
-        </is>
-      </c>
-      <c r="J104" s="7" t="inlineStr">
-        <is>
-          <t>_open()  if !opened &amp;&amp; context.mounted</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
@@ -5195,16 +4201,6 @@
         </is>
       </c>
       <c r="H105" s="8" t="n"/>
-      <c r="I105" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/events/draft_event_preview_screen.dart:71</t>
-        </is>
-      </c>
-      <c r="J105" s="7" t="inlineStr">
-        <is>
-          <t>_load()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
@@ -5241,16 +4237,6 @@
         </is>
       </c>
       <c r="H106" s="8" t="n"/>
-      <c r="I106" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/events/organizer_events_screen.dart:65</t>
-        </is>
-      </c>
-      <c r="J106" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
@@ -5287,16 +4273,6 @@
         </is>
       </c>
       <c r="H107" s="8" t="n"/>
-      <c r="I107" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/events/organizer_events_screen.dart:68</t>
-        </is>
-      </c>
-      <c r="J107" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n">
@@ -5333,16 +4309,6 @@
         </is>
       </c>
       <c r="H108" s="8" t="n"/>
-      <c r="I108" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/events/event_card.dart:331</t>
-        </is>
-      </c>
-      <c r="J108" s="7" t="inlineStr">
-        <is>
-          <t>build()  if context.mounted</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
@@ -5379,16 +4345,6 @@
         </is>
       </c>
       <c r="H109" s="8" t="n"/>
-      <c r="I109" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/events/event_card.dart:332</t>
-        </is>
-      </c>
-      <c r="J109" s="7" t="inlineStr">
-        <is>
-          <t>build()  if context.mounted</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
@@ -5425,16 +4381,6 @@
         </is>
       </c>
       <c r="H110" s="8" t="n"/>
-      <c r="I110" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/events/participant_events_screen.dart:41</t>
-        </is>
-      </c>
-      <c r="J110" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n">
@@ -5471,16 +4417,6 @@
         </is>
       </c>
       <c r="H111" s="8" t="n"/>
-      <c r="I111" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/events/participant_events_screen.dart:44</t>
-        </is>
-      </c>
-      <c r="J111" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n">
@@ -5517,16 +4453,6 @@
         </is>
       </c>
       <c r="H112" s="8" t="n"/>
-      <c r="I112" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/events/participant_events_screen.dart:82</t>
-        </is>
-      </c>
-      <c r="J112" s="7" t="inlineStr">
-        <is>
-          <t>build()  if events.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n">
@@ -5563,16 +4489,6 @@
         </is>
       </c>
       <c r="H113" s="8" t="n"/>
-      <c r="I113" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/family/family_manage_screens.dart:265</t>
-        </is>
-      </c>
-      <c r="J113" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if !fieldsOk || !sideOk</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n">
@@ -5609,16 +4525,6 @@
         </is>
       </c>
       <c r="H114" s="8" t="n"/>
-      <c r="I114" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/family/family_manage_screens.dart:270</t>
-        </is>
-      </c>
-      <c r="J114" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if eventId == null</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
@@ -5655,16 +4561,6 @@
         </is>
       </c>
       <c r="H115" s="8" t="n"/>
-      <c r="I115" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/family/family_settings_screen.dart:83</t>
-        </is>
-      </c>
-      <c r="J115" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
@@ -5701,16 +4597,6 @@
         </is>
       </c>
       <c r="H116" s="8" t="n"/>
-      <c r="I116" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/family/family_settings_screen.dart:131</t>
-        </is>
-      </c>
-      <c r="J116" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
@@ -5747,16 +4633,6 @@
         </is>
       </c>
       <c r="H117" s="8" t="n"/>
-      <c r="I117" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/family/family_settings_screen.dart:204</t>
-        </is>
-      </c>
-      <c r="J117" s="7" t="inlineStr">
-        <is>
-          <t>build()  if label == 'Name' &amp;&amp; !v</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n">
@@ -5793,16 +4669,6 @@
         </is>
       </c>
       <c r="H118" s="8" t="n"/>
-      <c r="I118" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/family/organizer_family_screen.dart:233</t>
-        </is>
-      </c>
-      <c r="J118" s="7" t="inlineStr">
-        <is>
-          <t>_body()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n">
@@ -5839,16 +4705,6 @@
         </is>
       </c>
       <c r="H119" s="8" t="n"/>
-      <c r="I119" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/family/organizer_family_screen.dart:236</t>
-        </is>
-      </c>
-      <c r="J119" s="7" t="inlineStr">
-        <is>
-          <t>_body()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n">
@@ -5885,16 +4741,6 @@
         </is>
       </c>
       <c r="H120" s="8" t="n"/>
-      <c r="I120" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/family/family_screen.dart:100</t>
-        </is>
-      </c>
-      <c r="J120" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n">
@@ -5931,16 +4777,6 @@
         </is>
       </c>
       <c r="H121" s="8" t="n"/>
-      <c r="I121" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/family/family_screen.dart:103</t>
-        </is>
-      </c>
-      <c r="J121" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n">
@@ -5977,16 +4813,6 @@
         </is>
       </c>
       <c r="H122" s="8" t="n"/>
-      <c r="I122" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/family/family_screen.dart:184</t>
-        </is>
-      </c>
-      <c r="J122" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n">
@@ -6023,16 +4849,6 @@
         </is>
       </c>
       <c r="H123" s="8" t="n"/>
-      <c r="I123" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/family/family_screen.dart:185</t>
-        </is>
-      </c>
-      <c r="J123" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="n">
@@ -6069,16 +4885,6 @@
         </is>
       </c>
       <c r="H124" s="8" t="n"/>
-      <c r="I124" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_categories_screen.dart:133</t>
-        </is>
-      </c>
-      <c r="J124" s="7" t="inlineStr">
-        <is>
-          <t>_delete()  if category.itemCount &gt; 0</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n">
@@ -6115,16 +4921,6 @@
         </is>
       </c>
       <c r="H125" s="8" t="n"/>
-      <c r="I125" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_categories_screen.dart:157</t>
-        </is>
-      </c>
-      <c r="J125" s="7" t="inlineStr">
-        <is>
-          <t>_download()</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="n">
@@ -6161,16 +4957,6 @@
         </is>
       </c>
       <c r="H126" s="8" t="n"/>
-      <c r="I126" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_categories_screen.dart:158</t>
-        </is>
-      </c>
-      <c r="J126" s="7" t="inlineStr">
-        <is>
-          <t>_download()</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n">
@@ -6207,16 +4993,6 @@
         </is>
       </c>
       <c r="H127" s="8" t="n"/>
-      <c r="I127" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_categories_screen.dart:176</t>
-        </is>
-      </c>
-      <c r="J127" s="7" t="inlineStr">
-        <is>
-          <t>_download()  if saved &gt; 0</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n">
@@ -6253,16 +5029,6 @@
         </is>
       </c>
       <c r="H128" s="8" t="n"/>
-      <c r="I128" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_categories_screen.dart:179</t>
-        </is>
-      </c>
-      <c r="J128" s="7" t="inlineStr">
-        <is>
-          <t>_download()  if saved &gt; 0</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n">
@@ -6299,16 +5065,6 @@
         </is>
       </c>
       <c r="H129" s="8" t="n"/>
-      <c r="I129" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_categories_screen.dart:228</t>
-        </is>
-      </c>
-      <c r="J129" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n">
@@ -6345,16 +5101,6 @@
         </is>
       </c>
       <c r="H130" s="8" t="n"/>
-      <c r="I130" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_category_form_screen.dart:95</t>
-        </is>
-      </c>
-      <c r="J130" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if name.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n">
@@ -6391,16 +5137,6 @@
         </is>
       </c>
       <c r="H131" s="8" t="n"/>
-      <c r="I131" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_category_form_screen.dart:193</t>
-        </is>
-      </c>
-      <c r="J131" s="7" t="inlineStr">
-        <is>
-          <t>build()  if nameMissing</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n">
@@ -6437,16 +5173,6 @@
         </is>
       </c>
       <c r="H132" s="8" t="n"/>
-      <c r="I132" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_media_screen.dart:88</t>
-        </is>
-      </c>
-      <c r="J132" s="7" t="inlineStr">
-        <is>
-          <t>_removePicked()  if ids.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n">
@@ -6483,16 +5209,6 @@
         </is>
       </c>
       <c r="H133" s="8" t="n"/>
-      <c r="I133" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_media_screen.dart:89</t>
-        </is>
-      </c>
-      <c r="J133" s="7" t="inlineStr">
-        <is>
-          <t>_removePicked()  if ids.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n">
@@ -6529,16 +5245,6 @@
         </is>
       </c>
       <c r="H134" s="8" t="n"/>
-      <c r="I134" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_media_screen.dart:120</t>
-        </is>
-      </c>
-      <c r="J134" s="7" t="inlineStr">
-        <is>
-          <t>_removePicked()  if failed == 0</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n">
@@ -6575,16 +5281,6 @@
         </is>
       </c>
       <c r="H135" s="8" t="n"/>
-      <c r="I135" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_media_screen.dart:149</t>
-        </is>
-      </c>
-      <c r="J135" s="7" t="inlineStr">
-        <is>
-          <t>_upload()  if usage.photos.isFull &amp;&amp; usage.videos.isFull</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="n">
@@ -6621,16 +5317,6 @@
         </is>
       </c>
       <c r="H136" s="8" t="n"/>
-      <c r="I136" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_media_screen.dart:157</t>
-        </is>
-      </c>
-      <c r="J136" s="7" t="inlineStr">
-        <is>
-          <t>_upload()  if usage.storageFull</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n">
@@ -6667,16 +5353,6 @@
         </is>
       </c>
       <c r="H137" s="8" t="n"/>
-      <c r="I137" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_media_screen.dart:417</t>
-        </is>
-      </c>
-      <c r="J137" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n">
@@ -6713,16 +5389,6 @@
         </is>
       </c>
       <c r="H138" s="8" t="n"/>
-      <c r="I138" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_photo_flow.dart:195</t>
-        </is>
-      </c>
-      <c r="J138" s="7" t="inlineStr">
-        <is>
-          <t>_apply()  if bytes == null</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n">
@@ -6759,16 +5425,6 @@
         </is>
       </c>
       <c r="H139" s="8" t="n"/>
-      <c r="I139" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_photo_flow.dart:232</t>
-        </is>
-      </c>
-      <c r="J139" s="7" t="inlineStr">
-        <is>
-          <t>_cropCurrent()  if !_dirty</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="n">
@@ -6805,16 +5461,6 @@
         </is>
       </c>
       <c r="H140" s="8" t="n"/>
-      <c r="I140" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_photo_flow.dart:256</t>
-        </is>
-      </c>
-      <c r="J140" s="7" t="inlineStr">
-        <is>
-          <t>_cropSingle()  if !_dirty</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n">
@@ -6851,16 +5497,6 @@
         </is>
       </c>
       <c r="H141" s="8" t="n"/>
-      <c r="I141" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_photo_flow.dart:296</t>
-        </is>
-      </c>
-      <c r="J141" s="7" t="inlineStr">
-        <is>
-          <t>photos()</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="n">
@@ -6897,16 +5533,6 @@
         </is>
       </c>
       <c r="H142" s="8" t="n"/>
-      <c r="I142" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_photo_flow.dart:298</t>
-        </is>
-      </c>
-      <c r="J142" s="7" t="inlineStr">
-        <is>
-          <t>photos()</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n">
@@ -6943,16 +5569,6 @@
         </is>
       </c>
       <c r="H143" s="8" t="n"/>
-      <c r="I143" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_photo_flow.dart:300</t>
-        </is>
-      </c>
-      <c r="J143" s="7" t="inlineStr">
-        <is>
-          <t>photos()</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="n">
@@ -6989,16 +5605,6 @@
         </is>
       </c>
       <c r="H144" s="8" t="n"/>
-      <c r="I144" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_photo_flow.dart:381</t>
-        </is>
-      </c>
-      <c r="J144" s="7" t="inlineStr">
-        <is>
-          <t>_editor()  if snap.hasError</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n">
@@ -7035,16 +5641,6 @@
         </is>
       </c>
       <c r="H145" s="8" t="n"/>
-      <c r="I145" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:170</t>
-        </is>
-      </c>
-      <c r="J145" s="7" t="inlineStr">
-        <is>
-          <t>_pickVideo()  if room != null &amp;&amp; _videos.length &gt;= room</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="n">
@@ -7081,16 +5677,6 @@
         </is>
       </c>
       <c r="H146" s="8" t="n"/>
-      <c r="I146" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:172</t>
-        </is>
-      </c>
-      <c r="J146" s="7" t="inlineStr">
-        <is>
-          <t>_pickVideo()  if room != null &amp;&amp; _videos.length &gt;= room</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n">
@@ -7127,16 +5713,6 @@
         </is>
       </c>
       <c r="H147" s="8" t="n"/>
-      <c r="I147" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:184</t>
-        </is>
-      </c>
-      <c r="J147" s="7" t="inlineStr">
-        <is>
-          <t>_pickVideo()  if !const {'mp4', 'webm', 'mov'}.contains(ext)</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="n">
@@ -7173,16 +5749,6 @@
         </is>
       </c>
       <c r="H148" s="8" t="n"/>
-      <c r="I148" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:217</t>
-        </is>
-      </c>
-      <c r="J148" s="7" t="inlineStr">
-        <is>
-          <t>_pickVideo()  if out == null || !mounted</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="n">
@@ -7219,16 +5785,6 @@
         </is>
       </c>
       <c r="H149" s="8" t="n"/>
-      <c r="I149" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:228</t>
-        </is>
-      </c>
-      <c r="J149" s="7" t="inlineStr">
-        <is>
-          <t>_pickVideo()  if finalSize &gt; widget.maxVideoBytes</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="n">
@@ -7265,16 +5821,6 @@
         </is>
       </c>
       <c r="H150" s="8" t="n"/>
-      <c r="I150" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:241</t>
-        </is>
-      </c>
-      <c r="J150" s="7" t="inlineStr">
-        <is>
-          <t>_pickVideo()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="n">
@@ -7311,16 +5857,6 @@
         </is>
       </c>
       <c r="H151" s="8" t="n"/>
-      <c r="I151" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:325</t>
-        </is>
-      </c>
-      <c r="J151" s="7" t="inlineStr">
-        <is>
-          <t>_pick()  if room != null &amp;&amp; _photoCount &gt;= room</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="n">
@@ -7357,16 +5893,6 @@
         </is>
       </c>
       <c r="H152" s="8" t="n"/>
-      <c r="I152" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:326</t>
-        </is>
-      </c>
-      <c r="J152" s="7" t="inlineStr">
-        <is>
-          <t>_pick()  if room != null &amp;&amp; _photoCount &gt;= room</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="n">
@@ -7403,16 +5929,6 @@
         </is>
       </c>
       <c r="H153" s="8" t="n"/>
-      <c r="I153" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:343</t>
-        </is>
-      </c>
-      <c r="J153" s="7" t="inlineStr">
-        <is>
-          <t>_pick()  if left != null &amp;&amp; picked.length &gt; left</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="n">
@@ -7449,16 +5965,6 @@
         </is>
       </c>
       <c r="H154" s="8" t="n"/>
-      <c r="I154" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:379</t>
-        </is>
-      </c>
-      <c r="J154" s="7" t="inlineStr">
-        <is>
-          <t>_pick()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="n">
@@ -7495,16 +6001,6 @@
         </is>
       </c>
       <c r="H155" s="8" t="n"/>
-      <c r="I155" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:390</t>
-        </is>
-      </c>
-      <c r="J155" s="7" t="inlineStr">
-        <is>
-          <t>_upload()  if _paths.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" s="6" t="n">
@@ -7541,16 +6037,6 @@
         </is>
       </c>
       <c r="H156" s="8" t="n"/>
-      <c r="I156" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_upload_screen.dart:454</t>
-        </is>
-      </c>
-      <c r="J156" s="7" t="inlineStr">
-        <is>
-          <t>noun()</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="n">
@@ -7587,16 +6073,6 @@
         </is>
       </c>
       <c r="H157" s="8" t="n"/>
-      <c r="I157" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_video_player.dart:84</t>
-        </is>
-      </c>
-      <c r="J157" s="7" t="inlineStr">
-        <is>
-          <t>build()  if _failed</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" s="6" t="n">
@@ -7633,16 +6109,6 @@
         </is>
       </c>
       <c r="H158" s="8" t="n"/>
-      <c r="I158" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_widgets.dart:432</t>
-        </is>
-      </c>
-      <c r="J158" s="7" t="inlineStr">
-        <is>
-          <t>saveGalleryItem()  if context.mounted</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n">
@@ -7679,16 +6145,6 @@
         </is>
       </c>
       <c r="H159" s="8" t="n"/>
-      <c r="I159" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_widgets.dart:446</t>
-        </is>
-      </c>
-      <c r="J159" s="7" t="inlineStr">
-        <is>
-          <t>saveGalleryItem()  if context.mounted</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n">
@@ -7725,16 +6181,6 @@
         </is>
       </c>
       <c r="H160" s="8" t="n"/>
-      <c r="I160" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_widgets.dart:464</t>
-        </is>
-      </c>
-      <c r="J160" s="7" t="inlineStr">
-        <is>
-          <t>saveGalleryItems()  if context.mounted</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n">
@@ -7771,16 +6217,6 @@
         </is>
       </c>
       <c r="H161" s="8" t="n"/>
-      <c r="I161" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/gallery_widgets.dart:495</t>
-        </is>
-      </c>
-      <c r="J161" s="7" t="inlineStr">
-        <is>
-          <t>shareGalleryItem()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="n">
@@ -7817,16 +6253,6 @@
         </is>
       </c>
       <c r="H162" s="8" t="n"/>
-      <c r="I162" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/gallery/video_trim_screen.dart:132</t>
-        </is>
-      </c>
-      <c r="J162" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="n">
@@ -7863,16 +6289,6 @@
         </is>
       </c>
       <c r="H163" s="8" t="n"/>
-      <c r="I163" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/gallery/gallery_screen.dart:103</t>
-        </is>
-      </c>
-      <c r="J163" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" s="6" t="n">
@@ -7909,16 +6325,6 @@
         </is>
       </c>
       <c r="H164" s="8" t="n"/>
-      <c r="I164" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/gallery/gallery_screen.dart:109</t>
-        </is>
-      </c>
-      <c r="J164" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="n">
@@ -7955,16 +6361,6 @@
         </is>
       </c>
       <c r="H165" s="8" t="n"/>
-      <c r="I165" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_address_fields.dart:91</t>
-        </is>
-      </c>
-      <c r="J165" s="7" t="inlineStr">
-        <is>
-          <t>_pickState()  if widget.country.text.trim().isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" s="6" t="n">
@@ -8001,16 +6397,6 @@
         </is>
       </c>
       <c r="H166" s="8" t="n"/>
-      <c r="I166" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_address_fields.dart:124</t>
-        </is>
-      </c>
-      <c r="J166" s="7" t="inlineStr">
-        <is>
-          <t>_pickCity()  if widget.state.text.trim().isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="n">
@@ -8047,16 +6433,6 @@
         </is>
       </c>
       <c r="H167" s="8" t="n"/>
-      <c r="I167" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_address_fields.dart:146</t>
-        </is>
-      </c>
-      <c r="J167" s="7" t="inlineStr">
-        <is>
-          <t>_pickPostal()  if widget.city.text.trim().isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" s="6" t="n">
@@ -8093,16 +6469,6 @@
         </is>
       </c>
       <c r="H168" s="8" t="n"/>
-      <c r="I168" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_details_screen.dart:41</t>
-        </is>
-      </c>
-      <c r="J168" s="7" t="inlineStr">
-        <is>
-          <t>_delete()</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n">
@@ -8139,16 +6505,6 @@
         </is>
       </c>
       <c r="H169" s="8" t="n"/>
-      <c r="I169" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_body.dart:358</t>
-        </is>
-      </c>
-      <c r="J169" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" s="6" t="n">
@@ -8185,16 +6541,6 @@
         </is>
       </c>
       <c r="H170" s="8" t="n"/>
-      <c r="I170" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_body.dart:424</t>
-        </is>
-      </c>
-      <c r="J170" s="7" t="inlineStr">
-        <is>
-          <t>build()  if t.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="n">
@@ -8231,16 +6577,6 @@
         </is>
       </c>
       <c r="H171" s="8" t="n"/>
-      <c r="I171" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_body.dart:462</t>
-        </is>
-      </c>
-      <c r="J171" s="7" t="inlineStr">
-        <is>
-          <t>build()  if _sideMissing</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="6" t="n">
@@ -8277,16 +6613,6 @@
         </is>
       </c>
       <c r="H172" s="8" t="n"/>
-      <c r="I172" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_body.dart:623</t>
-        </is>
-      </c>
-      <c r="J172" s="7" t="inlineStr">
-        <is>
-          <t>_relationshipField()  if match != null &amp;&amp; (_relationship == null || _relationship!.id == 0)</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n">
@@ -8323,16 +6649,6 @@
         </is>
       </c>
       <c r="H173" s="8" t="n"/>
-      <c r="I173" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_body.dart:658</t>
-        </is>
-      </c>
-      <c r="J173" s="7" t="inlineStr">
-        <is>
-          <t>_relationshipField()</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" s="6" t="n">
@@ -8369,16 +6685,6 @@
         </is>
       </c>
       <c r="H174" s="8" t="n"/>
-      <c r="I174" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_body.dart:677</t>
-        </is>
-      </c>
-      <c r="J174" s="7" t="inlineStr">
-        <is>
-          <t>_foodField()</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="n">
@@ -8415,16 +6721,6 @@
         </is>
       </c>
       <c r="H175" s="8" t="n"/>
-      <c r="I175" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_screen.dart:226</t>
-        </is>
-      </c>
-      <c r="J175" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if _first.text.trim().isEmpty || _mobile.text.trim().isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" s="6" t="n">
@@ -8461,16 +6757,6 @@
         </is>
       </c>
       <c r="H176" s="8" t="n"/>
-      <c r="I176" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_screen.dart:231</t>
-        </is>
-      </c>
-      <c r="J176" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if email.isNotEmpty &amp;&amp; !_emailShape.hasMatch(email)</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="n">
@@ -8507,16 +6793,6 @@
         </is>
       </c>
       <c r="H177" s="8" t="n"/>
-      <c r="I177" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_screen.dart:312</t>
-        </is>
-      </c>
-      <c r="J177" s="7" t="inlineStr">
-        <is>
-          <t>build()  if cap != null &amp;&amp; cap.full</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="n">
@@ -8553,16 +6829,6 @@
         </is>
       </c>
       <c r="H178" s="8" t="n"/>
-      <c r="I178" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_screen.dart:313</t>
-        </is>
-      </c>
-      <c r="J178" s="7" t="inlineStr">
-        <is>
-          <t>build()  if cap != null &amp;&amp; cap.full</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n">
@@ -8599,16 +6865,6 @@
         </is>
       </c>
       <c r="H179" s="8" t="n"/>
-      <c r="I179" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_screen.dart:594</t>
-        </is>
-      </c>
-      <c r="J179" s="7" t="inlineStr">
-        <is>
-          <t>_relationshipField()</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="n">
@@ -8645,16 +6901,6 @@
         </is>
       </c>
       <c r="H180" s="8" t="n"/>
-      <c r="I180" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_form_screen.dart:633</t>
-        </is>
-      </c>
-      <c r="J180" s="7" t="inlineStr">
-        <is>
-          <t>_foodField()</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="n">
@@ -8691,16 +6937,6 @@
         </is>
       </c>
       <c r="H181" s="8" t="n"/>
-      <c r="I181" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_groups_screen.dart:129</t>
-        </is>
-      </c>
-      <c r="J181" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="n">
@@ -8737,16 +6973,6 @@
         </is>
       </c>
       <c r="H182" s="8" t="n"/>
-      <c r="I182" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_groups_screen.dart:136</t>
-        </is>
-      </c>
-      <c r="J182" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="n">
@@ -8783,16 +7009,6 @@
         </is>
       </c>
       <c r="H183" s="8" t="n"/>
-      <c r="I183" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_groups_screen.dart:332</t>
-        </is>
-      </c>
-      <c r="J183" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if name.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" s="6" t="n">
@@ -8829,16 +7045,6 @@
         </is>
       </c>
       <c r="H184" s="8" t="n"/>
-      <c r="I184" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_groups_screen.dart:431</t>
-        </is>
-      </c>
-      <c r="J184" s="7" t="inlineStr">
-        <is>
-          <t>build()  if missing</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="n">
@@ -8875,16 +7081,6 @@
         </is>
       </c>
       <c r="H185" s="8" t="n"/>
-      <c r="I185" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_list_screen.dart:100</t>
-        </is>
-      </c>
-      <c r="J185" s="7" t="inlineStr">
-        <is>
-          <t>_delete()</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" s="6" t="n">
@@ -8921,16 +7117,6 @@
         </is>
       </c>
       <c r="H186" s="8" t="n"/>
-      <c r="I186" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_list_screen.dart:276</t>
-        </is>
-      </c>
-      <c r="J186" s="7" t="inlineStr">
-        <is>
-          <t>_body()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="n">
@@ -8967,16 +7153,6 @@
         </is>
       </c>
       <c r="H187" s="8" t="n"/>
-      <c r="I187" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_list_screen.dart:284</t>
-        </is>
-      </c>
-      <c r="J187" s="7" t="inlineStr">
-        <is>
-          <t>_body()</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" s="6" t="n">
@@ -9013,16 +7189,6 @@
         </is>
       </c>
       <c r="H188" s="8" t="n"/>
-      <c r="I188" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_list_screen.dart:292</t>
-        </is>
-      </c>
-      <c r="J188" s="7" t="inlineStr">
-        <is>
-          <t>_body()</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="n">
@@ -9059,16 +7225,6 @@
         </is>
       </c>
       <c r="H189" s="8" t="n"/>
-      <c r="I189" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_widgets.dart:30</t>
-        </is>
-      </c>
-      <c r="J189" s="7" t="inlineStr">
-        <is>
-          <t>_open()  if number.isEmpty || number.startsWith('+')</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="n">
@@ -9105,16 +7261,6 @@
         </is>
       </c>
       <c r="H190" s="8" t="n"/>
-      <c r="I190" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_widgets.dart:33</t>
-        </is>
-      </c>
-      <c r="J190" s="7" t="inlineStr">
-        <is>
-          <t>_open()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="n">
@@ -9151,16 +7297,6 @@
         </is>
       </c>
       <c r="H191" s="8" t="n"/>
-      <c r="I191" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_widgets.dart:40</t>
-        </is>
-      </c>
-      <c r="J191" s="7" t="inlineStr">
-        <is>
-          <t>callGuest()  if number.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="n">
@@ -9197,16 +7333,6 @@
         </is>
       </c>
       <c r="H192" s="8" t="n"/>
-      <c r="I192" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_widgets.dart:49</t>
-        </is>
-      </c>
-      <c r="J192" s="7" t="inlineStr">
-        <is>
-          <t>whatsAppGuest()  if digits.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="n">
@@ -9243,16 +7369,6 @@
         </is>
       </c>
       <c r="H193" s="8" t="n"/>
-      <c r="I193" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/guests/guest_widgets.dart:58</t>
-        </is>
-      </c>
-      <c r="J193" s="7" t="inlineStr">
-        <is>
-          <t>emailGuest()  if email.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="n">
@@ -9289,16 +7405,6 @@
         </is>
       </c>
       <c r="H194" s="8" t="n"/>
-      <c r="I194" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/home/organizer_home_screen.dart:37</t>
-        </is>
-      </c>
-      <c r="J194" s="7" t="inlineStr">
-        <is>
-          <t>_soon()</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="n">
@@ -9335,16 +7441,6 @@
         </is>
       </c>
       <c r="H195" s="8" t="n"/>
-      <c r="I195" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/home/organizer_home_screen.dart:50</t>
-        </is>
-      </c>
-      <c r="J195" s="7" t="inlineStr">
-        <is>
-          <t>_forEvent()  if events.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" s="6" t="n">
@@ -9381,16 +7477,6 @@
         </is>
       </c>
       <c r="H196" s="8" t="n"/>
-      <c r="I196" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/home/quick_actions_section.dart:152</t>
-        </is>
-      </c>
-      <c r="J196" s="7" t="inlineStr">
-        <is>
-          <t>_done()  if !mounted</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="n">
@@ -9427,16 +7513,6 @@
         </is>
       </c>
       <c r="H197" s="8" t="n"/>
-      <c r="I197" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/home/quick_actions_section.dart:176</t>
-        </is>
-      </c>
-      <c r="J197" s="7" t="inlineStr">
-        <is>
-          <t>_open()  if t == null || t.soon</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" s="6" t="n">
@@ -9473,16 +7549,6 @@
         </is>
       </c>
       <c r="H198" s="8" t="n"/>
-      <c r="I198" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/home/quick_actions_section.dart:289</t>
-        </is>
-      </c>
-      <c r="J198" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.hasError &amp;&amp; data == null</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="n">
@@ -9519,16 +7585,6 @@
         </is>
       </c>
       <c r="H199" s="8" t="n"/>
-      <c r="I199" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/home/quick_actions_section.dart:310</t>
-        </is>
-      </c>
-      <c r="J199" s="7" t="inlineStr">
-        <is>
-          <t>build()  if addable.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" s="6" t="n">
@@ -9565,16 +7621,6 @@
         </is>
       </c>
       <c r="H200" s="8" t="n"/>
-      <c r="I200" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/invitation/invitation_screen.dart:110</t>
-        </is>
-      </c>
-      <c r="J200" s="7" t="inlineStr">
-        <is>
-          <t>_shareImage()</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="n">
@@ -9611,16 +7657,6 @@
         </is>
       </c>
       <c r="H201" s="8" t="n"/>
-      <c r="I201" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/invitation/invitation_screen.dart:122</t>
-        </is>
-      </c>
-      <c r="J201" s="7" t="inlineStr">
-        <is>
-          <t>_saveToGallery()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" s="6" t="n">
@@ -9657,16 +7693,6 @@
         </is>
       </c>
       <c r="H202" s="8" t="n"/>
-      <c r="I202" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/invitation/invitation_screen.dart:131</t>
-        </is>
-      </c>
-      <c r="J202" s="7" t="inlineStr">
-        <is>
-          <t>_saveToGallery()  if bytes == null</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="n">
@@ -9703,16 +7729,6 @@
         </is>
       </c>
       <c r="H203" s="8" t="n"/>
-      <c r="I203" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/invite/invite_shared.dart:322</t>
-        </is>
-      </c>
-      <c r="J203" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" s="6" t="n">
@@ -9749,16 +7765,6 @@
         </is>
       </c>
       <c r="H204" s="8" t="n"/>
-      <c r="I204" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/invite/invite_shared.dart:325</t>
-        </is>
-      </c>
-      <c r="J204" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="n">
@@ -9795,16 +7801,6 @@
         </is>
       </c>
       <c r="H205" s="8" t="n"/>
-      <c r="I205" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/invite/invite_shared.dart:334</t>
-        </is>
-      </c>
-      <c r="J205" s="7" t="inlineStr">
-        <is>
-          <t>build()  if guests.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" s="6" t="n">
@@ -9841,16 +7837,6 @@
         </is>
       </c>
       <c r="H206" s="8" t="n"/>
-      <c r="I206" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/invitation_card_screen.dart:242</t>
-        </is>
-      </c>
-      <c r="J206" s="7" t="inlineStr">
-        <is>
-          <t>_saveDesign()  if _themeCode == null</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="n">
@@ -9887,16 +7873,6 @@
         </is>
       </c>
       <c r="H207" s="8" t="n"/>
-      <c r="I207" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/invitation_card_screen.dart:355</t>
-        </is>
-      </c>
-      <c r="J207" s="7" t="inlineStr">
-        <is>
-          <t>_saveContent()</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="n">
@@ -9933,16 +7909,6 @@
         </is>
       </c>
       <c r="H208" s="8" t="n"/>
-      <c r="I208" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/invitation_card_screen.dart:359</t>
-        </is>
-      </c>
-      <c r="J208" s="7" t="inlineStr">
-        <is>
-          <t>_saveContent()  if !RegExp(r'^[^@\s]+@[^@\s]+\.[^@\s]+$').hasMatch(_email.text.trim())</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="n">
@@ -9979,16 +7945,6 @@
         </is>
       </c>
       <c r="H209" s="8" t="n"/>
-      <c r="I209" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/invitation_card_screen.dart:597</t>
-        </is>
-      </c>
-      <c r="J209" s="7" t="inlineStr">
-        <is>
-          <t>_pickColor()</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="n">
@@ -10025,16 +7981,6 @@
         </is>
       </c>
       <c r="H210" s="8" t="n"/>
-      <c r="I210" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/invitation_card_screen.dart:597</t>
-        </is>
-      </c>
-      <c r="J210" s="7" t="inlineStr">
-        <is>
-          <t>_pickColor()</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="n">
@@ -10071,16 +8017,6 @@
         </is>
       </c>
       <c r="H211" s="8" t="n"/>
-      <c r="I211" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/invitation_card_screen.dart:883</t>
-        </is>
-      </c>
-      <c r="J211" s="7" t="inlineStr">
-        <is>
-          <t>step()</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" s="6" t="n">
@@ -10117,16 +8053,6 @@
         </is>
       </c>
       <c r="H212" s="8" t="n"/>
-      <c r="I212" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/invitation_card_screen.dart:994</t>
-        </is>
-      </c>
-      <c r="J212" s="7" t="inlineStr">
-        <is>
-          <t>field()  if (e.startDate ?? '').isNotEmpty &amp;&amp; e.status != 'draft'</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="n">
@@ -10163,16 +8089,6 @@
         </is>
       </c>
       <c r="H213" s="8" t="n"/>
-      <c r="I213" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/organizer_invitation_screen.dart:107</t>
-        </is>
-      </c>
-      <c r="J213" s="7" t="inlineStr">
-        <is>
-          <t>_shareImage()</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" s="6" t="n">
@@ -10209,16 +8125,6 @@
         </is>
       </c>
       <c r="H214" s="8" t="n"/>
-      <c r="I214" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_email_screen.dart:71</t>
-        </is>
-      </c>
-      <c r="J214" s="7" t="inlineStr">
-        <is>
-          <t>_next()  if _step == 0 &amp;&amp; _selected.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="n">
@@ -10255,16 +8161,6 @@
         </is>
       </c>
       <c r="H215" s="8" t="n"/>
-      <c r="I215" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:130</t>
-        </is>
-      </c>
-      <c r="J215" s="7" t="inlineStr">
-        <is>
-          <t>_afterGuests()  if _selected.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="n">
@@ -10301,16 +8197,6 @@
         </is>
       </c>
       <c r="H216" s="8" t="n"/>
-      <c r="I216" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:173</t>
-        </is>
-      </c>
-      <c r="J216" s="7" t="inlineStr">
-        <is>
-          <t>_whatsappTo()  if number.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="n">
@@ -10347,16 +8233,6 @@
         </is>
       </c>
       <c r="H217" s="8" t="n"/>
-      <c r="I217" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:186</t>
-        </is>
-      </c>
-      <c r="J217" s="7" t="inlineStr">
-        <is>
-          <t>_whatsappTo()  if opened</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" s="6" t="n">
@@ -10393,16 +8269,6 @@
         </is>
       </c>
       <c r="H218" s="8" t="n"/>
-      <c r="I218" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:216</t>
-        </is>
-      </c>
-      <c r="J218" s="7" t="inlineStr">
-        <is>
-          <t>_emailAll()  if to.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="n">
@@ -10439,16 +8305,6 @@
         </is>
       </c>
       <c r="H219" s="8" t="n"/>
-      <c r="I219" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:228</t>
-        </is>
-      </c>
-      <c r="J219" s="7" t="inlineStr">
-        <is>
-          <t>enc()  if !opened</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" s="6" t="n">
@@ -10485,16 +8341,6 @@
         </is>
       </c>
       <c r="H220" s="8" t="n"/>
-      <c r="I220" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:246</t>
-        </is>
-      </c>
-      <c r="J220" s="7" t="inlineStr">
-        <is>
-          <t>_galleryAccess()</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="n">
@@ -10531,16 +8377,6 @@
         </is>
       </c>
       <c r="H221" s="8" t="n"/>
-      <c r="I221" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:265</t>
-        </is>
-      </c>
-      <c r="J221" s="7" t="inlineStr">
-        <is>
-          <t>_shareVia()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" s="6" t="n">
@@ -10577,16 +8413,6 @@
         </is>
       </c>
       <c r="H222" s="8" t="n"/>
-      <c r="I222" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:282</t>
-        </is>
-      </c>
-      <c r="J222" s="7" t="inlineStr">
-        <is>
-          <t>_qrAction()  if share</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="n">
@@ -10623,16 +8449,6 @@
         </is>
       </c>
       <c r="H223" s="8" t="n"/>
-      <c r="I223" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:292</t>
-        </is>
-      </c>
-      <c r="J223" s="7" t="inlineStr">
-        <is>
-          <t>_qrAction()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" s="6" t="n">
@@ -10669,16 +8485,6 @@
         </is>
       </c>
       <c r="H224" s="8" t="n"/>
-      <c r="I224" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:326</t>
-        </is>
-      </c>
-      <c r="J224" s="7" t="inlineStr">
-        <is>
-          <t>_cardAction()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="n">
@@ -10715,16 +8521,6 @@
         </is>
       </c>
       <c r="H225" s="8" t="n"/>
-      <c r="I225" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:662</t>
-        </is>
-      </c>
-      <c r="J225" s="7" t="inlineStr">
-        <is>
-          <t>qrBlock()</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" s="6" t="n">
@@ -10761,16 +8557,6 @@
         </is>
       </c>
       <c r="H226" s="8" t="n"/>
-      <c r="I226" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_invitation_flow.dart:982</t>
-        </is>
-      </c>
-      <c r="J226" s="7" t="inlineStr">
-        <is>
-          <t>_sentView()</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="n">
@@ -10807,16 +8593,6 @@
         </is>
       </c>
       <c r="H227" s="8" t="n"/>
-      <c r="I227" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_qr_screen.dart:500</t>
-        </is>
-      </c>
-      <c r="J227" s="7" t="inlineStr">
-        <is>
-          <t>_qrCard()</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" s="6" t="n">
@@ -10853,16 +8629,6 @@
         </is>
       </c>
       <c r="H228" s="8" t="n"/>
-      <c r="I228" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_sms_screen.dart:36</t>
-        </is>
-      </c>
-      <c r="J228" s="7" t="inlineStr">
-        <is>
-          <t>_next()  if _step == 0 &amp;&amp; _selected.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="n">
@@ -10899,16 +8665,6 @@
         </is>
       </c>
       <c r="H229" s="8" t="n"/>
-      <c r="I229" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/invite/share_whatsapp_screen.dart:59</t>
-        </is>
-      </c>
-      <c r="J229" s="7" t="inlineStr">
-        <is>
-          <t>_next()  if _step == 0 &amp;&amp; _selected.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" s="6" t="n">
@@ -10945,16 +8701,6 @@
         </is>
       </c>
       <c r="H230" s="8" t="n"/>
-      <c r="I230" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/registration_screen.dart:172</t>
-        </is>
-      </c>
-      <c r="J230" s="7" t="inlineStr">
-        <is>
-          <t>_sendOtp()  if mobile.length &lt; 7</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="n">
@@ -10991,16 +8737,6 @@
         </is>
       </c>
       <c r="H231" s="8" t="n"/>
-      <c r="I231" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/registration_screen.dart:202</t>
-        </is>
-      </c>
-      <c r="J231" s="7" t="inlineStr">
-        <is>
-          <t>_sendOtp()  if challenge.delivered</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" s="6" t="n">
@@ -11037,16 +8773,6 @@
         </is>
       </c>
       <c r="H232" s="8" t="n"/>
-      <c r="I232" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/registration_screen.dart:203</t>
-        </is>
-      </c>
-      <c r="J232" s="7" t="inlineStr">
-        <is>
-          <t>_sendOtp()  if challenge.delivered</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="n">
@@ -11083,16 +8809,6 @@
         </is>
       </c>
       <c r="H233" s="8" t="n"/>
-      <c r="I233" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/registration_screen.dart:243</t>
-        </is>
-      </c>
-      <c r="J233" s="7" t="inlineStr">
-        <is>
-          <t>_next()  if !_verified</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" s="6" t="n">
@@ -11129,16 +8845,6 @@
         </is>
       </c>
       <c r="H234" s="8" t="n"/>
-      <c r="I234" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/scan_qr_screen.dart:160</t>
-        </is>
-      </c>
-      <c r="J234" s="7" t="inlineStr">
-        <is>
-          <t>_startScanner()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="n">
@@ -11175,16 +8881,6 @@
         </is>
       </c>
       <c r="H235" s="8" t="n"/>
-      <c r="I235" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/scan_qr_screen.dart:270</t>
-        </is>
-      </c>
-      <c r="J235" s="7" t="inlineStr">
-        <is>
-          <t>_useToken()  if details.participantsFull</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" s="6" t="n">
@@ -11221,16 +8917,6 @@
         </is>
       </c>
       <c r="H236" s="8" t="n"/>
-      <c r="I236" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/scan_qr_screen.dart:272</t>
-        </is>
-      </c>
-      <c r="J236" s="7" t="inlineStr">
-        <is>
-          <t>_useToken()  if details.participantsFull</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="n">
@@ -11267,16 +8953,6 @@
         </is>
       </c>
       <c r="H237" s="8" t="n"/>
-      <c r="I237" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/scan_qr_screen.dart:274</t>
-        </is>
-      </c>
-      <c r="J237" s="7" t="inlineStr">
-        <is>
-          <t>_useToken()  if details.participantsFull</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" s="6" t="n">
@@ -11313,16 +8989,6 @@
         </is>
       </c>
       <c r="H238" s="8" t="n"/>
-      <c r="I238" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/scan_qr_screen.dart:360</t>
-        </is>
-      </c>
-      <c r="J238" s="7" t="inlineStr">
-        <is>
-          <t>_pickImageFromGallery()  if raw != null &amp;&amp; raw.isNotEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="n">
@@ -11359,16 +9025,6 @@
         </is>
       </c>
       <c r="H239" s="8" t="n"/>
-      <c r="I239" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/scan_qr_screen.dart:367</t>
-        </is>
-      </c>
-      <c r="J239" s="7" t="inlineStr">
-        <is>
-          <t>_pickImageFromGallery()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" s="6" t="n">
@@ -11405,16 +9061,6 @@
         </is>
       </c>
       <c r="H240" s="8" t="n"/>
-      <c r="I240" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/scan_qr_screen.dart:381</t>
-        </is>
-      </c>
-      <c r="J240" s="7" t="inlineStr">
-        <is>
-          <t>_enterManually()</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" s="6" t="n">
@@ -11451,16 +9097,6 @@
         </is>
       </c>
       <c r="H241" s="8" t="n"/>
-      <c r="I241" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/join/scan_qr_screen.dart:388</t>
-        </is>
-      </c>
-      <c r="J241" s="7" t="inlineStr">
-        <is>
-          <t>_enterManually()</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" s="6" t="n">
@@ -11497,16 +9133,6 @@
         </is>
       </c>
       <c r="H242" s="8" t="n"/>
-      <c r="I242" s="7" t="inlineStr">
-        <is>
-          <t>features/common/notifications/notifications_screen.dart:258</t>
-        </is>
-      </c>
-      <c r="J242" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="n">
@@ -11543,16 +9169,6 @@
         </is>
       </c>
       <c r="H243" s="8" t="n"/>
-      <c r="I243" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:320</t>
-        </is>
-      </c>
-      <c r="J243" s="7" t="inlineStr">
-        <is>
-          <t>_required()</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" s="6" t="n">
@@ -11589,16 +9205,6 @@
         </is>
       </c>
       <c r="H244" s="8" t="n"/>
-      <c r="I244" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:324</t>
-        </is>
-      </c>
-      <c r="J244" s="7" t="inlineStr">
-        <is>
-          <t>_collect()  if !(_formKey.currentState?.validate() ?? false)</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="n">
@@ -11635,16 +9241,6 @@
         </is>
       </c>
       <c r="H245" s="8" t="n"/>
-      <c r="I245" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:359</t>
-        </is>
-      </c>
-      <c r="J245" s="7" t="inlineStr">
-        <is>
-          <t>_leave()  if _title.text.trim().isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="n">
@@ -11681,16 +9277,6 @@
         </is>
       </c>
       <c r="H246" s="8" t="n"/>
-      <c r="I246" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:647</t>
-        </is>
-      </c>
-      <c r="J246" s="7" t="inlineStr">
-        <is>
-          <t>_next()  if o == null</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="n">
@@ -11727,16 +9313,6 @@
         </is>
       </c>
       <c r="H247" s="8" t="n"/>
-      <c r="I247" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:651</t>
-        </is>
-      </c>
-      <c r="J247" s="7" t="inlineStr">
-        <is>
-          <t>_next()  if d.audience == NoticeAudience.specific &amp;&amp; d.participantIds.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" s="6" t="n">
@@ -11773,16 +9349,6 @@
         </is>
       </c>
       <c r="H248" s="8" t="n"/>
-      <c r="I248" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:657</t>
-        </is>
-      </c>
-      <c r="J248" s="7" t="inlineStr">
-        <is>
-          <t>_next()  if d.audience == NoticeAudience.groups &amp;&amp; d.sides.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" s="6" t="n">
@@ -11819,16 +9385,6 @@
         </is>
       </c>
       <c r="H249" s="8" t="n"/>
-      <c r="I249" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:662</t>
-        </is>
-      </c>
-      <c r="J249" s="7" t="inlineStr">
-        <is>
-          <t>_next()  if _reach(o) == 0</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" s="6" t="n">
@@ -11865,16 +9421,6 @@
         </is>
       </c>
       <c r="H250" s="8" t="n"/>
-      <c r="I250" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:795</t>
-        </is>
-      </c>
-      <c r="J250" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" s="6" t="n">
@@ -11911,16 +9457,6 @@
         </is>
       </c>
       <c r="H251" s="8" t="n"/>
-      <c r="I251" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:1047</t>
-        </is>
-      </c>
-      <c r="J251" s="7" t="inlineStr">
-        <is>
-          <t>_next()  if widget.draft.channels.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" s="6" t="n">
@@ -11957,16 +9493,6 @@
         </is>
       </c>
       <c r="H252" s="8" t="n"/>
-      <c r="I252" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:1131</t>
-        </is>
-      </c>
-      <c r="J252" s="7" t="inlineStr">
-        <is>
-          <t>build()  if when == null</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" s="6" t="n">
@@ -12003,16 +9529,6 @@
         </is>
       </c>
       <c r="H253" s="8" t="n"/>
-      <c r="I253" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_compose_flow.dart:1139</t>
-        </is>
-      </c>
-      <c r="J253" s="7" t="inlineStr">
-        <is>
-          <t>build()  if !instant.isAfter(DateTime.now())</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" s="6" t="n">
@@ -12049,16 +9565,6 @@
         </is>
       </c>
       <c r="H254" s="8" t="n"/>
-      <c r="I254" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/notification_widgets.dart:235</t>
-        </is>
-      </c>
-      <c r="J254" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="n">
@@ -12095,16 +9601,6 @@
         </is>
       </c>
       <c r="H255" s="8" t="n"/>
-      <c r="I255" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/organizer_notifications_screen.dart:55</t>
-        </is>
-      </c>
-      <c r="J255" s="7" t="inlineStr">
-        <is>
-          <t>_delete()</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" s="6" t="n">
@@ -12141,16 +9637,6 @@
         </is>
       </c>
       <c r="H256" s="8" t="n"/>
-      <c r="I256" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/organizer_notifications_screen.dart:56</t>
-        </is>
-      </c>
-      <c r="J256" s="7" t="inlineStr">
-        <is>
-          <t>_delete()</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="n">
@@ -12187,16 +9673,6 @@
         </is>
       </c>
       <c r="H257" s="8" t="n"/>
-      <c r="I257" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/organizer_notifications_screen.dart:167</t>
-        </is>
-      </c>
-      <c r="J257" s="7" t="inlineStr">
-        <is>
-          <t>_message()</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" s="6" t="n">
@@ -12233,16 +9709,6 @@
         </is>
       </c>
       <c r="H258" s="8" t="n"/>
-      <c r="I258" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/notifications/organizer_notifications_screen.dart:203</t>
-        </is>
-      </c>
-      <c r="J258" s="7" t="inlineStr">
-        <is>
-          <t>build()  if !async.hasValue</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="n">
@@ -12279,16 +9745,6 @@
         </is>
       </c>
       <c r="H259" s="8" t="n"/>
-      <c r="I259" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/add_participant_screen.dart:56</t>
-        </is>
-      </c>
-      <c r="J259" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if !(_formKey.currentState?.validate() ?? false)</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" s="6" t="n">
@@ -12325,16 +9781,6 @@
         </is>
       </c>
       <c r="H260" s="8" t="n"/>
-      <c r="I260" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/add_participant_screen.dart:62</t>
-        </is>
-      </c>
-      <c r="J260" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if eventId == null</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" s="6" t="n">
@@ -12371,16 +9817,6 @@
         </is>
       </c>
       <c r="H261" s="8" t="n"/>
-      <c r="I261" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/add_participant_screen.dart:176</t>
-        </is>
-      </c>
-      <c r="J261" s="7" t="inlineStr">
-        <is>
-          <t>build()  if cap != null &amp;&amp; cap.full</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" s="6" t="n">
@@ -12417,16 +9853,6 @@
         </is>
       </c>
       <c r="H262" s="8" t="n"/>
-      <c r="I262" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/add_participant_screen.dart:177</t>
-        </is>
-      </c>
-      <c r="J262" s="7" t="inlineStr">
-        <is>
-          <t>build()  if cap != null &amp;&amp; cap.full</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" s="6" t="n">
@@ -12463,16 +9889,6 @@
         </is>
       </c>
       <c r="H263" s="8" t="n"/>
-      <c r="I263" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participant_details_screen.dart:79</t>
-        </is>
-      </c>
-      <c r="J263" s="7" t="inlineStr">
-        <is>
-          <t>_remove()  if p == null || _isRemoving</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" s="6" t="n">
@@ -12509,16 +9925,6 @@
         </is>
       </c>
       <c r="H264" s="8" t="n"/>
-      <c r="I264" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participant_details_screen.dart:94</t>
-        </is>
-      </c>
-      <c r="J264" s="7" t="inlineStr">
-        <is>
-          <t>_remove()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" s="6" t="n">
@@ -12555,16 +9961,6 @@
         </is>
       </c>
       <c r="H265" s="8" t="n"/>
-      <c r="I265" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participant_details_screen.dart:111</t>
-        </is>
-      </c>
-      <c r="J265" s="7" t="inlineStr">
-        <is>
-          <t>_launchExternal()  if await canLaunchUrl(uri)</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" s="6" t="n">
@@ -12601,16 +9997,6 @@
         </is>
       </c>
       <c r="H266" s="8" t="n"/>
-      <c r="I266" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participant_details_screen.dart:114</t>
-        </is>
-      </c>
-      <c r="J266" s="7" t="inlineStr">
-        <is>
-          <t>_launchExternal()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" s="6" t="n">
@@ -12647,16 +10033,6 @@
         </is>
       </c>
       <c r="H267" s="8" t="n"/>
-      <c r="I267" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participant_details_screen.dart:144</t>
-        </is>
-      </c>
-      <c r="J267" s="7" t="inlineStr">
-        <is>
-          <t>_onRsvpChanged()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" s="6" t="n">
@@ -12693,16 +10069,6 @@
         </is>
       </c>
       <c r="H268" s="8" t="n"/>
-      <c r="I268" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participant_details_screen.dart:754</t>
-        </is>
-      </c>
-      <c r="J268" s="7" t="inlineStr">
-        <is>
-          <t>_actionBar()  if numOnly.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="n">
@@ -12739,16 +10105,6 @@
         </is>
       </c>
       <c r="H269" s="8" t="n"/>
-      <c r="I269" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participant_details_screen.dart:767</t>
-        </is>
-      </c>
-      <c r="J269" s="7" t="inlineStr">
-        <is>
-          <t>_actionBar()  if _cleanPhone.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" s="6" t="n">
@@ -12785,16 +10141,6 @@
         </is>
       </c>
       <c r="H270" s="8" t="n"/>
-      <c r="I270" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participant_details_screen.dart:780</t>
-        </is>
-      </c>
-      <c r="J270" s="7" t="inlineStr">
-        <is>
-          <t>_actionBar()  if _cleanPhone.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" s="6" t="n">
@@ -12831,16 +10177,6 @@
         </is>
       </c>
       <c r="H271" s="8" t="n"/>
-      <c r="I271" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participants_screen.dart:306</t>
-        </is>
-      </c>
-      <c r="J271" s="7" t="inlineStr">
-        <is>
-          <t>_body()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" s="6" t="n">
@@ -12877,16 +10213,6 @@
         </is>
       </c>
       <c r="H272" s="8" t="n"/>
-      <c r="I272" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participants_screen.dart:314</t>
-        </is>
-      </c>
-      <c r="J272" s="7" t="inlineStr">
-        <is>
-          <t>_body()</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" s="6" t="n">
@@ -12923,16 +10249,6 @@
         </is>
       </c>
       <c r="H273" s="8" t="n"/>
-      <c r="I273" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participants_screen.dart:322</t>
-        </is>
-      </c>
-      <c r="J273" s="7" t="inlineStr">
-        <is>
-          <t>_body()</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" s="6" t="n">
@@ -12969,16 +10285,6 @@
         </is>
       </c>
       <c r="H274" s="8" t="n"/>
-      <c r="I274" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/organizer_participants_screen.dart:353</t>
-        </is>
-      </c>
-      <c r="J274" s="7" t="inlineStr">
-        <is>
-          <t>_body()</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" s="6" t="n">
@@ -13015,16 +10321,6 @@
         </is>
       </c>
       <c r="H275" s="8" t="n"/>
-      <c r="I275" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/participant_manage_screens.dart:422</t>
-        </is>
-      </c>
-      <c r="J275" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if _awaitingGuest</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" s="6" t="n">
@@ -13061,16 +10357,6 @@
         </is>
       </c>
       <c r="H276" s="8" t="n"/>
-      <c r="I276" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/participant_manage_screens.dart:429</t>
-        </is>
-      </c>
-      <c r="J276" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if !fieldsOk || !sideOk</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" s="6" t="n">
@@ -13107,16 +10393,6 @@
         </is>
       </c>
       <c r="H277" s="8" t="n"/>
-      <c r="I277" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/participant_manage_screens.dart:434</t>
-        </is>
-      </c>
-      <c r="J277" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if eventId == null</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" s="6" t="n">
@@ -13153,16 +10429,6 @@
         </is>
       </c>
       <c r="H278" s="8" t="n"/>
-      <c r="I278" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/participant_manage_screens.dart:743</t>
-        </is>
-      </c>
-      <c r="J278" s="7" t="inlineStr">
-        <is>
-          <t>_guestPicker()  if _guestMissing</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" s="6" t="n">
@@ -13199,16 +10465,6 @@
         </is>
       </c>
       <c r="H279" s="8" t="n"/>
-      <c r="I279" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/participant_manage_screens.dart:1261</t>
-        </is>
-      </c>
-      <c r="J279" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" s="6" t="n">
@@ -13245,16 +10501,6 @@
         </is>
       </c>
       <c r="H280" s="8" t="n"/>
-      <c r="I280" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/participant_manage_screens.dart:1273</t>
-        </is>
-      </c>
-      <c r="J280" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" s="6" t="n">
@@ -13291,16 +10537,6 @@
         </is>
       </c>
       <c r="H281" s="8" t="n"/>
-      <c r="I281" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/participant_manage_screens.dart:1276</t>
-        </is>
-      </c>
-      <c r="J281" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" s="6" t="n">
@@ -13337,16 +10573,6 @@
         </is>
       </c>
       <c r="H282" s="8" t="n"/>
-      <c r="I282" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/participant_settings_screen.dart:96</t>
-        </is>
-      </c>
-      <c r="J282" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" s="6" t="n">
@@ -13383,16 +10609,6 @@
         </is>
       </c>
       <c r="H283" s="8" t="n"/>
-      <c r="I283" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/participant_settings_screen.dart:135</t>
-        </is>
-      </c>
-      <c r="J283" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" s="6" t="n">
@@ -13429,16 +10645,6 @@
         </is>
       </c>
       <c r="H284" s="8" t="n"/>
-      <c r="I284" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/participants/participant_settings_screen.dart:208</t>
-        </is>
-      </c>
-      <c r="J284" s="7" t="inlineStr">
-        <is>
-          <t>build()  if label == 'Name' &amp;&amp; !v</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" s="6" t="n">
@@ -13475,16 +10681,6 @@
         </is>
       </c>
       <c r="H285" s="8" t="n"/>
-      <c r="I285" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/participants/participant_details_screen.dart:67</t>
-        </is>
-      </c>
-      <c r="J285" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" s="6" t="n">
@@ -13521,16 +10717,6 @@
         </is>
       </c>
       <c r="H286" s="8" t="n"/>
-      <c r="I286" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/participants/participant_details_screen.dart:69</t>
-        </is>
-      </c>
-      <c r="J286" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" s="6" t="n">
@@ -13567,16 +10753,6 @@
         </is>
       </c>
       <c r="H287" s="8" t="n"/>
-      <c r="I287" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/participants/participants_screen.dart:151</t>
-        </is>
-      </c>
-      <c r="J287" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" s="6" t="n">
@@ -13613,16 +10789,6 @@
         </is>
       </c>
       <c r="H288" s="8" t="n"/>
-      <c r="I288" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/participants/participants_screen.dart:154</t>
-        </is>
-      </c>
-      <c r="J288" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" s="6" t="n">
@@ -13659,16 +10825,6 @@
         </is>
       </c>
       <c r="H289" s="8" t="n"/>
-      <c r="I289" s="7" t="inlineStr">
-        <is>
-          <t>features/common/permission/permission_detail_screen.dart:68</t>
-        </is>
-      </c>
-      <c r="J289" s="7" t="inlineStr">
-        <is>
-          <t>_allow()</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" s="6" t="n">
@@ -13705,16 +10861,6 @@
         </is>
       </c>
       <c r="H290" s="8" t="n"/>
-      <c r="I290" s="7" t="inlineStr">
-        <is>
-          <t>features/common/permission/permission_screen.dart:74</t>
-        </is>
-      </c>
-      <c r="J290" s="7" t="inlineStr">
-        <is>
-          <t>createState()</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" s="6" t="n">
@@ -13751,16 +10897,6 @@
         </is>
       </c>
       <c r="H291" s="8" t="n"/>
-      <c r="I291" s="7" t="inlineStr">
-        <is>
-          <t>features/common/permission/permission_screen.dart:96</t>
-        </is>
-      </c>
-      <c r="J291" s="7" t="inlineStr">
-        <is>
-          <t>createState()</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" s="6" t="n">
@@ -13797,16 +10933,6 @@
         </is>
       </c>
       <c r="H292" s="8" t="n"/>
-      <c r="I292" s="7" t="inlineStr">
-        <is>
-          <t>features/common/permission/permission_screen.dart:236</t>
-        </is>
-      </c>
-      <c r="J292" s="7" t="inlineStr">
-        <is>
-          <t>_allowAndContinue()</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" s="6" t="n">
@@ -13843,16 +10969,6 @@
         </is>
       </c>
       <c r="H293" s="8" t="n"/>
-      <c r="I293" s="7" t="inlineStr">
-        <is>
-          <t>features/common/permission/permission_screen.dart:290</t>
-        </is>
-      </c>
-      <c r="J293" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" s="6" t="n">
@@ -13889,16 +11005,6 @@
         </is>
       </c>
       <c r="H294" s="8" t="n"/>
-      <c r="I294" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/plan/plan_config_screen.dart:136</t>
-        </is>
-      </c>
-      <c r="J294" s="7" t="inlineStr">
-        <is>
-          <t>_comingSoon()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" s="6" t="n">
@@ -13935,16 +11041,6 @@
         </is>
       </c>
       <c r="H295" s="8" t="n"/>
-      <c r="I295" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/plan/plan_config_screen.dart:180</t>
-        </is>
-      </c>
-      <c r="J295" s="7" t="inlineStr">
-        <is>
-          <t>waiting()</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" s="6" t="n">
@@ -13981,16 +11077,6 @@
         </is>
       </c>
       <c r="H296" s="8" t="n"/>
-      <c r="I296" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/rsvp/rsvp_preview_screen.dart:199</t>
-        </is>
-      </c>
-      <c r="J296" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" s="6" t="n">
@@ -14027,16 +11113,6 @@
         </is>
       </c>
       <c r="H297" s="8" t="n"/>
-      <c r="I297" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/rsvp/rsvp_responses_screen.dart:137</t>
-        </is>
-      </c>
-      <c r="J297" s="7" t="inlineStr">
-        <is>
-          <t>_body()  if async.hasError</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" s="6" t="n">
@@ -14073,16 +11149,6 @@
         </is>
       </c>
       <c r="H298" s="8" t="n"/>
-      <c r="I298" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/rsvp/rsvp_responses_screen.dart:140</t>
-        </is>
-      </c>
-      <c r="J298" s="7" t="inlineStr">
-        <is>
-          <t>_body()  if async.hasError</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" s="6" t="n">
@@ -14119,16 +11185,6 @@
         </is>
       </c>
       <c r="H299" s="8" t="n"/>
-      <c r="I299" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/rsvp/rsvp_responses_screen.dart:725</t>
-        </is>
-      </c>
-      <c r="J299" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if _answer == null</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" s="6" t="n">
@@ -14165,16 +11221,6 @@
         </is>
       </c>
       <c r="H300" s="8" t="n"/>
-      <c r="I300" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/rsvp/rsvp_responses_screen.dart:776</t>
-        </is>
-      </c>
-      <c r="J300" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" s="6" t="n">
@@ -14211,16 +11257,6 @@
         </is>
       </c>
       <c r="H301" s="8" t="n"/>
-      <c r="I301" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/rsvp/rsvp_responses_screen.dart:1110</t>
-        </is>
-      </c>
-      <c r="J301" s="7" t="inlineStr">
-        <is>
-          <t>delete()</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" s="6" t="n">
@@ -14257,16 +11293,6 @@
         </is>
       </c>
       <c r="H302" s="8" t="n"/>
-      <c r="I302" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/rsvp/rsvp_settings_screen.dart:96</t>
-        </is>
-      </c>
-      <c r="J302" s="7" t="inlineStr">
-        <is>
-          <t>_pickDeadline()  if last.isBefore(today)</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" s="6" t="n">
@@ -14303,16 +11329,6 @@
         </is>
       </c>
       <c r="H303" s="8" t="n"/>
-      <c r="I303" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/rsvp/rsvp_settings_screen.dart:192</t>
-        </is>
-      </c>
-      <c r="J303" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" s="6" t="n">
@@ -14349,16 +11365,6 @@
         </is>
       </c>
       <c r="H304" s="8" t="n"/>
-      <c r="I304" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/rsvp/rsvp_settings_screen.dart:341</t>
-        </is>
-      </c>
-      <c r="J304" s="7" t="inlineStr">
-        <is>
-          <t>_responseOptions()</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" s="6" t="n">
@@ -14395,16 +11401,6 @@
         </is>
       </c>
       <c r="H305" s="8" t="n"/>
-      <c r="I305" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/rsvp/rsvp_screen.dart:73</t>
-        </is>
-      </c>
-      <c r="J305" s="7" t="inlineStr">
-        <is>
-          <t>_submit()  if _response == null</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" s="6" t="n">
@@ -14441,16 +11437,6 @@
         </is>
       </c>
       <c r="H306" s="8" t="n"/>
-      <c r="I306" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/rsvp/rsvp_screen.dart:135</t>
-        </is>
-      </c>
-      <c r="J306" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" s="6" t="n">
@@ -14487,16 +11473,6 @@
         </is>
       </c>
       <c r="H307" s="8" t="n"/>
-      <c r="I307" s="7" t="inlineStr">
-        <is>
-          <t>features/participant/rsvp/rsvp_screen.dart:138</t>
-        </is>
-      </c>
-      <c r="J307" s="7" t="inlineStr">
-        <is>
-          <t>build()  if async.isFailed</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" s="6" t="n">
@@ -14533,16 +11509,6 @@
         </is>
       </c>
       <c r="H308" s="8" t="n"/>
-      <c r="I308" s="7" t="inlineStr">
-        <is>
-          <t>features/common/settings/settings_screen.dart:69</t>
-        </is>
-      </c>
-      <c r="J308" s="7" t="inlineStr">
-        <is>
-          <t>_confirmLogout()</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" s="6" t="n">
@@ -14579,16 +11545,6 @@
         </is>
       </c>
       <c r="H309" s="8" t="n"/>
-      <c r="I309" s="7" t="inlineStr">
-        <is>
-          <t>features/common/settings/settings_screen.dart:70</t>
-        </is>
-      </c>
-      <c r="J309" s="7" t="inlineStr">
-        <is>
-          <t>_confirmLogout()</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" s="6" t="n">
@@ -14625,16 +11581,6 @@
         </is>
       </c>
       <c r="H310" s="8" t="n"/>
-      <c r="I310" s="7" t="inlineStr">
-        <is>
-          <t>shared/widgets/app_image_pick_crop.dart:82</t>
-        </is>
-      </c>
-      <c r="J310" s="7" t="inlineStr">
-        <is>
-          <t>pick()  if context.mounted</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" s="6" t="n">
@@ -14671,16 +11617,6 @@
         </is>
       </c>
       <c r="H311" s="8" t="n"/>
-      <c r="I311" s="7" t="inlineStr">
-        <is>
-          <t>shared/widgets/connection_banner.dart:80</t>
-        </is>
-      </c>
-      <c r="J311" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" s="6" t="n">
@@ -14717,16 +11653,6 @@
         </is>
       </c>
       <c r="H312" s="8" t="n"/>
-      <c r="I312" s="7" t="inlineStr">
-        <is>
-          <t>shared/widgets/offline_sync_button.dart:69</t>
-        </is>
-      </c>
-      <c r="J312" s="7" t="inlineStr">
-        <is>
-          <t>_download()  if !ok &amp;&amp; context.mounted</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" s="6" t="n">
@@ -14763,16 +11689,6 @@
         </is>
       </c>
       <c r="H313" s="8" t="n"/>
-      <c r="I313" s="7" t="inlineStr">
-        <is>
-          <t>shared/widgets/offline_sync_button.dart:90</t>
-        </is>
-      </c>
-      <c r="J313" s="7" t="inlineStr">
-        <is>
-          <t>build()  if sync == null || !sync.needsDownload</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" s="6" t="n">
@@ -14809,16 +11725,6 @@
         </is>
       </c>
       <c r="H314" s="8" t="n"/>
-      <c r="I314" s="7" t="inlineStr">
-        <is>
-          <t>shared/widgets/plan_usage_card.dart:93</t>
-        </is>
-      </c>
-      <c r="J314" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" s="6" t="n">
@@ -14855,16 +11761,6 @@
         </is>
       </c>
       <c r="H315" s="8" t="n"/>
-      <c r="I315" s="7" t="inlineStr">
-        <is>
-          <t>shared/widgets/plan_usage_card.dart:228</t>
-        </is>
-      </c>
-      <c r="J315" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" s="6" t="n">
@@ -14901,16 +11797,6 @@
         </is>
       </c>
       <c r="H316" s="8" t="n"/>
-      <c r="I316" s="7" t="inlineStr">
-        <is>
-          <t>shared/widgets/plan_usage_card.dart:233</t>
-        </is>
-      </c>
-      <c r="J316" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" s="6" t="n">
@@ -14947,16 +11833,6 @@
         </is>
       </c>
       <c r="H317" s="8" t="n"/>
-      <c r="I317" s="7" t="inlineStr">
-        <is>
-          <t>shared/widgets/plan_usage_card.dart:234</t>
-        </is>
-      </c>
-      <c r="J317" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" s="6" t="n">
@@ -14993,16 +11869,6 @@
         </is>
       </c>
       <c r="H318" s="8" t="n"/>
-      <c r="I318" s="7" t="inlineStr">
-        <is>
-          <t>shared/widgets/plan_usage_card.dart:276</t>
-        </is>
-      </c>
-      <c r="J318" s="7" t="inlineStr">
-        <is>
-          <t>_count()</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" s="6" t="n">
@@ -15039,16 +11905,6 @@
         </is>
       </c>
       <c r="H319" s="8" t="n"/>
-      <c r="I319" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/shell/organizer_bottom_nav.dart:50</t>
-        </is>
-      </c>
-      <c r="J319" s="7" t="inlineStr">
-        <is>
-          <t>createEvent()  if !hasPlan</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" s="6" t="n">
@@ -15085,16 +11941,6 @@
         </is>
       </c>
       <c r="H320" s="8" t="n"/>
-      <c r="I320" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/social/create_post_screen.dart:31</t>
-        </is>
-      </c>
-      <c r="J320" s="7" t="inlineStr">
-        <is>
-          <t>_post()  if _text.text.trim().isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" s="6" t="n">
@@ -15131,16 +11977,6 @@
         </is>
       </c>
       <c r="H321" s="8" t="n"/>
-      <c r="I321" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/splash/splash_editor_flow.dart:221</t>
-        </is>
-      </c>
-      <c r="J321" s="7" t="inlineStr">
-        <is>
-          <t>_save()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" s="6" t="n">
@@ -15177,16 +12013,6 @@
         </is>
       </c>
       <c r="H322" s="8" t="n"/>
-      <c r="I322" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/splash/splash_editor_flow.dart:239</t>
-        </is>
-      </c>
-      <c r="J322" s="7" t="inlineStr">
-        <is>
-          <t>_openColorPicker()</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" s="6" t="n">
@@ -15223,16 +12049,6 @@
         </is>
       </c>
       <c r="H323" s="8" t="n"/>
-      <c r="I323" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/splash/splash_editor_flow.dart:239</t>
-        </is>
-      </c>
-      <c r="J323" s="7" t="inlineStr">
-        <is>
-          <t>_openColorPicker()</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" s="6" t="n">
@@ -15269,16 +12085,6 @@
         </is>
       </c>
       <c r="H324" s="8" t="n"/>
-      <c r="I324" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/splash/splash_editor_flow.dart:291</t>
-        </is>
-      </c>
-      <c r="J324" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" s="6" t="n">
@@ -15315,16 +12121,6 @@
         </is>
       </c>
       <c r="H325" s="8" t="n"/>
-      <c r="I325" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:50</t>
-        </is>
-      </c>
-      <c r="J325" s="7" t="inlineStr">
-        <is>
-          <t>emailNotVerified()</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" s="6" t="n">
@@ -15361,16 +12157,6 @@
         </is>
       </c>
       <c r="H326" s="8" t="n"/>
-      <c r="I326" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:52</t>
-        </is>
-      </c>
-      <c r="J326" s="7" t="inlineStr">
-        <is>
-          <t>emailNotVerified()</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" s="6" t="n">
@@ -15407,16 +12193,6 @@
         </is>
       </c>
       <c r="H327" s="8" t="n"/>
-      <c r="I327" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:54</t>
-        </is>
-      </c>
-      <c r="J327" s="7" t="inlineStr">
-        <is>
-          <t>emailNotVerified()</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" s="6" t="n">
@@ -15453,16 +12229,6 @@
         </is>
       </c>
       <c r="H328" s="8" t="n"/>
-      <c r="I328" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:64</t>
-        </is>
-      </c>
-      <c r="J328" s="7" t="inlineStr">
-        <is>
-          <t>accountLocked()</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" s="6" t="n">
@@ -15499,16 +12265,6 @@
         </is>
       </c>
       <c r="H329" s="8" t="n"/>
-      <c r="I329" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:65</t>
-        </is>
-      </c>
-      <c r="J329" s="7" t="inlineStr">
-        <is>
-          <t>accountLocked()</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" s="6" t="n">
@@ -15545,16 +12301,6 @@
         </is>
       </c>
       <c r="H330" s="8" t="n"/>
-      <c r="I330" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:80</t>
-        </is>
-      </c>
-      <c r="J330" s="7" t="inlineStr">
-        <is>
-          <t>sessionExpired()</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" s="6" t="n">
@@ -15591,16 +12337,6 @@
         </is>
       </c>
       <c r="H331" s="8" t="n"/>
-      <c r="I331" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:82</t>
-        </is>
-      </c>
-      <c r="J331" s="7" t="inlineStr">
-        <is>
-          <t>sessionExpired()</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" s="6" t="n">
@@ -15637,16 +12373,6 @@
         </is>
       </c>
       <c r="H332" s="8" t="n"/>
-      <c r="I332" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:84</t>
-        </is>
-      </c>
-      <c r="J332" s="7" t="inlineStr">
-        <is>
-          <t>sessionExpired()</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" s="6" t="n">
@@ -15683,16 +12409,6 @@
         </is>
       </c>
       <c r="H333" s="8" t="n"/>
-      <c r="I333" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:93</t>
-        </is>
-      </c>
-      <c r="J333" s="7" t="inlineStr">
-        <is>
-          <t>accessDenied()</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" s="6" t="n">
@@ -15729,16 +12445,6 @@
         </is>
       </c>
       <c r="H334" s="8" t="n"/>
-      <c r="I334" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:94</t>
-        </is>
-      </c>
-      <c r="J334" s="7" t="inlineStr">
-        <is>
-          <t>accessDenied()</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" s="6" t="n">
@@ -15775,16 +12481,6 @@
         </is>
       </c>
       <c r="H335" s="8" t="n"/>
-      <c r="I335" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:105</t>
-        </is>
-      </c>
-      <c r="J335" s="7" t="inlineStr">
-        <is>
-          <t>noData()</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" s="6" t="n">
@@ -15821,16 +12517,6 @@
         </is>
       </c>
       <c r="H336" s="8" t="n"/>
-      <c r="I336" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:116</t>
-        </is>
-      </c>
-      <c r="J336" s="7" t="inlineStr">
-        <is>
-          <t>searchNoResult()</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" s="6" t="n">
@@ -15867,16 +12553,6 @@
         </is>
       </c>
       <c r="H337" s="8" t="n"/>
-      <c r="I337" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:117</t>
-        </is>
-      </c>
-      <c r="J337" s="7" t="inlineStr">
-        <is>
-          <t>searchNoResult()</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" s="6" t="n">
@@ -15913,16 +12589,6 @@
         </is>
       </c>
       <c r="H338" s="8" t="n"/>
-      <c r="I338" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:128</t>
-        </is>
-      </c>
-      <c r="J338" s="7" t="inlineStr">
-        <is>
-          <t>filterNoResult()</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" s="6" t="n">
@@ -15959,16 +12625,6 @@
         </is>
       </c>
       <c r="H339" s="8" t="n"/>
-      <c r="I339" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:129</t>
-        </is>
-      </c>
-      <c r="J339" s="7" t="inlineStr">
-        <is>
-          <t>filterNoResult()</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" s="6" t="n">
@@ -16005,16 +12661,6 @@
         </is>
       </c>
       <c r="H340" s="8" t="n"/>
-      <c r="I340" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:140</t>
-        </is>
-      </c>
-      <c r="J340" s="7" t="inlineStr">
-        <is>
-          <t>offline()</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" s="6" t="n">
@@ -16051,16 +12697,6 @@
         </is>
       </c>
       <c r="H341" s="8" t="n"/>
-      <c r="I341" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:141</t>
-        </is>
-      </c>
-      <c r="J341" s="7" t="inlineStr">
-        <is>
-          <t>offline()</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" s="6" t="n">
@@ -16097,16 +12733,6 @@
         </is>
       </c>
       <c r="H342" s="8" t="n"/>
-      <c r="I342" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:152</t>
-        </is>
-      </c>
-      <c r="J342" s="7" t="inlineStr">
-        <is>
-          <t>internetSlow()</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" s="6" t="n">
@@ -16143,16 +12769,6 @@
         </is>
       </c>
       <c r="H343" s="8" t="n"/>
-      <c r="I343" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:153</t>
-        </is>
-      </c>
-      <c r="J343" s="7" t="inlineStr">
-        <is>
-          <t>internetSlow()</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" s="6" t="n">
@@ -16189,16 +12805,6 @@
         </is>
       </c>
       <c r="H344" s="8" t="n"/>
-      <c r="I344" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:162</t>
-        </is>
-      </c>
-      <c r="J344" s="7" t="inlineStr">
-        <is>
-          <t>maintenance()</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" s="6" t="n">
@@ -16235,16 +12841,6 @@
         </is>
       </c>
       <c r="H345" s="8" t="n"/>
-      <c r="I345" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:163</t>
-        </is>
-      </c>
-      <c r="J345" s="7" t="inlineStr">
-        <is>
-          <t>maintenance()</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" s="6" t="n">
@@ -16281,16 +12877,6 @@
         </is>
       </c>
       <c r="H346" s="8" t="n"/>
-      <c r="I346" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:175</t>
-        </is>
-      </c>
-      <c r="J346" s="7" t="inlineStr">
-        <is>
-          <t>appUpdate()</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" s="6" t="n">
@@ -16327,16 +12913,6 @@
         </is>
       </c>
       <c r="H347" s="8" t="n"/>
-      <c r="I347" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:186</t>
-        </is>
-      </c>
-      <c r="J347" s="7" t="inlineStr">
-        <is>
-          <t>loading()</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" s="6" t="n">
@@ -16373,16 +12949,6 @@
         </is>
       </c>
       <c r="H348" s="8" t="n"/>
-      <c r="I348" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:187</t>
-        </is>
-      </c>
-      <c r="J348" s="7" t="inlineStr">
-        <is>
-          <t>loading()</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" s="6" t="n">
@@ -16419,16 +12985,6 @@
         </is>
       </c>
       <c r="H349" s="8" t="n"/>
-      <c r="I349" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:195</t>
-        </is>
-      </c>
-      <c r="J349" s="7" t="inlineStr">
-        <is>
-          <t>somethingWentWrong()</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" s="6" t="n">
@@ -16465,16 +13021,6 @@
         </is>
       </c>
       <c r="H350" s="8" t="n"/>
-      <c r="I350" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:197</t>
-        </is>
-      </c>
-      <c r="J350" s="7" t="inlineStr">
-        <is>
-          <t>somethingWentWrong()</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" s="6" t="n">
@@ -16511,16 +13057,6 @@
         </is>
       </c>
       <c r="H351" s="8" t="n"/>
-      <c r="I351" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:200</t>
-        </is>
-      </c>
-      <c r="J351" s="7" t="inlineStr">
-        <is>
-          <t>somethingWentWrong()</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" s="6" t="n">
@@ -16557,16 +13093,6 @@
         </is>
       </c>
       <c r="H352" s="8" t="n"/>
-      <c r="I352" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:206</t>
-        </is>
-      </c>
-      <c r="J352" s="7" t="inlineStr">
-        <is>
-          <t>underReview()</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" s="6" t="n">
@@ -16603,16 +13129,6 @@
         </is>
       </c>
       <c r="H353" s="8" t="n"/>
-      <c r="I353" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:208</t>
-        </is>
-      </c>
-      <c r="J353" s="7" t="inlineStr">
-        <is>
-          <t>underReview()</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" s="6" t="n">
@@ -16649,16 +13165,6 @@
         </is>
       </c>
       <c r="H354" s="8" t="n"/>
-      <c r="I354" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:219</t>
-        </is>
-      </c>
-      <c r="J354" s="7" t="inlineStr">
-        <is>
-          <t>paymentSuccess()</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" s="6" t="n">
@@ -16695,16 +13201,6 @@
         </is>
       </c>
       <c r="H355" s="8" t="n"/>
-      <c r="I355" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:220</t>
-        </is>
-      </c>
-      <c r="J355" s="7" t="inlineStr">
-        <is>
-          <t>paymentSuccess()</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" s="6" t="n">
@@ -16741,16 +13237,6 @@
         </is>
       </c>
       <c r="H356" s="8" t="n"/>
-      <c r="I356" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:231</t>
-        </is>
-      </c>
-      <c r="J356" s="7" t="inlineStr">
-        <is>
-          <t>paymentFailed()</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" s="6" t="n">
@@ -16787,16 +13273,6 @@
         </is>
       </c>
       <c r="H357" s="8" t="n"/>
-      <c r="I357" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:232</t>
-        </is>
-      </c>
-      <c r="J357" s="7" t="inlineStr">
-        <is>
-          <t>paymentFailed()</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" s="6" t="n">
@@ -16833,16 +13309,6 @@
         </is>
       </c>
       <c r="H358" s="8" t="n"/>
-      <c r="I358" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:244</t>
-        </is>
-      </c>
-      <c r="J358" s="7" t="inlineStr">
-        <is>
-          <t>paymentPending()</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" s="6" t="n">
@@ -16879,16 +13345,6 @@
         </is>
       </c>
       <c r="H359" s="8" t="n"/>
-      <c r="I359" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:246</t>
-        </is>
-      </c>
-      <c r="J359" s="7" t="inlineStr">
-        <is>
-          <t>paymentPending()</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" s="6" t="n">
@@ -16925,16 +13381,6 @@
         </is>
       </c>
       <c r="H360" s="8" t="n"/>
-      <c r="I360" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:257</t>
-        </is>
-      </c>
-      <c r="J360" s="7" t="inlineStr">
-        <is>
-          <t>bookingConfirmed()</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" s="6" t="n">
@@ -16971,16 +13417,6 @@
         </is>
       </c>
       <c r="H361" s="8" t="n"/>
-      <c r="I361" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:258</t>
-        </is>
-      </c>
-      <c r="J361" s="7" t="inlineStr">
-        <is>
-          <t>bookingConfirmed()</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" s="6" t="n">
@@ -17017,16 +13453,6 @@
         </is>
       </c>
       <c r="H362" s="8" t="n"/>
-      <c r="I362" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:270</t>
-        </is>
-      </c>
-      <c r="J362" s="7" t="inlineStr">
-        <is>
-          <t>bookingCancelled()</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" s="6" t="n">
@@ -17063,16 +13489,6 @@
         </is>
       </c>
       <c r="H363" s="8" t="n"/>
-      <c r="I363" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:271</t>
-        </is>
-      </c>
-      <c r="J363" s="7" t="inlineStr">
-        <is>
-          <t>bookingCancelled()</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" s="6" t="n">
@@ -17109,16 +13525,6 @@
         </is>
       </c>
       <c r="H364" s="8" t="n"/>
-      <c r="I364" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:281</t>
-        </is>
-      </c>
-      <c r="J364" s="7" t="inlineStr">
-        <is>
-          <t>siteVisitScheduled()</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" s="6" t="n">
@@ -17155,16 +13561,6 @@
         </is>
       </c>
       <c r="H365" s="8" t="n"/>
-      <c r="I365" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:282</t>
-        </is>
-      </c>
-      <c r="J365" s="7" t="inlineStr">
-        <is>
-          <t>siteVisitScheduled()</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" s="6" t="n">
@@ -17201,16 +13597,6 @@
         </is>
       </c>
       <c r="H366" s="8" t="n"/>
-      <c r="I366" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:294</t>
-        </is>
-      </c>
-      <c r="J366" s="7" t="inlineStr">
-        <is>
-          <t>documentUploaded()</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" s="6" t="n">
@@ -17247,16 +13633,6 @@
         </is>
       </c>
       <c r="H367" s="8" t="n"/>
-      <c r="I367" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:295</t>
-        </is>
-      </c>
-      <c r="J367" s="7" t="inlineStr">
-        <is>
-          <t>documentUploaded()</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" s="6" t="n">
@@ -17293,16 +13669,6 @@
         </is>
       </c>
       <c r="H368" s="8" t="n"/>
-      <c r="I368" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:307</t>
-        </is>
-      </c>
-      <c r="J368" s="7" t="inlineStr">
-        <is>
-          <t>documentUploadFailed()</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" s="6" t="n">
@@ -17339,16 +13705,6 @@
         </is>
       </c>
       <c r="H369" s="8" t="n"/>
-      <c r="I369" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:308</t>
-        </is>
-      </c>
-      <c r="J369" s="7" t="inlineStr">
-        <is>
-          <t>documentUploadFailed()</t>
-        </is>
-      </c>
     </row>
     <row r="370">
       <c r="A370" s="6" t="n">
@@ -17385,16 +13741,6 @@
         </is>
       </c>
       <c r="H370" s="8" t="n"/>
-      <c r="I370" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:311</t>
-        </is>
-      </c>
-      <c r="J370" s="7" t="inlineStr">
-        <is>
-          <t>documentUploadFailed()</t>
-        </is>
-      </c>
     </row>
     <row r="371">
       <c r="A371" s="6" t="n">
@@ -17431,16 +13777,6 @@
         </is>
       </c>
       <c r="H371" s="8" t="n"/>
-      <c r="I371" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:318</t>
-        </is>
-      </c>
-      <c r="J371" s="7" t="inlineStr">
-        <is>
-          <t>linkCopied()</t>
-        </is>
-      </c>
     </row>
     <row r="372">
       <c r="A372" s="6" t="n">
@@ -17477,16 +13813,6 @@
         </is>
       </c>
       <c r="H372" s="8" t="n"/>
-      <c r="I372" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:319</t>
-        </is>
-      </c>
-      <c r="J372" s="7" t="inlineStr">
-        <is>
-          <t>linkCopied()</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" s="6" t="n">
@@ -17523,16 +13849,6 @@
         </is>
       </c>
       <c r="H373" s="8" t="n"/>
-      <c r="I373" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:330</t>
-        </is>
-      </c>
-      <c r="J373" s="7" t="inlineStr">
-        <is>
-          <t>logoutSuccess()</t>
-        </is>
-      </c>
     </row>
     <row r="374">
       <c r="A374" s="6" t="n">
@@ -17569,16 +13885,6 @@
         </is>
       </c>
       <c r="H374" s="8" t="n"/>
-      <c r="I374" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:331</t>
-        </is>
-      </c>
-      <c r="J374" s="7" t="inlineStr">
-        <is>
-          <t>logoutSuccess()</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" s="6" t="n">
@@ -17615,16 +13921,6 @@
         </is>
       </c>
       <c r="H375" s="8" t="n"/>
-      <c r="I375" s="7" t="inlineStr">
-        <is>
-          <t>features/common/status/status_views.dart:332</t>
-        </is>
-      </c>
-      <c r="J375" s="7" t="inlineStr">
-        <is>
-          <t>logoutSuccess()</t>
-        </is>
-      </c>
     </row>
     <row r="376">
       <c r="A376" s="6" t="n">
@@ -17661,16 +13957,6 @@
         </is>
       </c>
       <c r="H376" s="8" t="n"/>
-      <c r="I376" s="7" t="inlineStr">
-        <is>
-          <t>features/common/theme/theme_screen.dart:378</t>
-        </is>
-      </c>
-      <c r="J376" s="7" t="inlineStr">
-        <is>
-          <t>_reset()</t>
-        </is>
-      </c>
     </row>
     <row r="377">
       <c r="A377" s="6" t="n">
@@ -17707,16 +13993,6 @@
         </is>
       </c>
       <c r="H377" s="8" t="n"/>
-      <c r="I377" s="7" t="inlineStr">
-        <is>
-          <t>features/common/theme/theme_screen.dart:379</t>
-        </is>
-      </c>
-      <c r="J377" s="7" t="inlineStr">
-        <is>
-          <t>_reset()</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" s="6" t="n">
@@ -17753,16 +14029,6 @@
         </is>
       </c>
       <c r="H378" s="8" t="n"/>
-      <c r="I378" s="7" t="inlineStr">
-        <is>
-          <t>features/common/theme/theme_screen.dart:762</t>
-        </is>
-      </c>
-      <c r="J378" s="7" t="inlineStr">
-        <is>
-          <t>_reset()</t>
-        </is>
-      </c>
     </row>
     <row r="379">
       <c r="A379" s="6" t="n">
@@ -17799,16 +14065,6 @@
         </is>
       </c>
       <c r="H379" s="8" t="n"/>
-      <c r="I379" s="7" t="inlineStr">
-        <is>
-          <t>features/common/theme/theme_screen.dart:763</t>
-        </is>
-      </c>
-      <c r="J379" s="7" t="inlineStr">
-        <is>
-          <t>_reset()</t>
-        </is>
-      </c>
     </row>
     <row r="380">
       <c r="A380" s="6" t="n">
@@ -17845,16 +14101,6 @@
         </is>
       </c>
       <c r="H380" s="8" t="n"/>
-      <c r="I380" s="7" t="inlineStr">
-        <is>
-          <t>features/common/theme/theme_screen.dart:1074</t>
-        </is>
-      </c>
-      <c r="J380" s="7" t="inlineStr">
-        <is>
-          <t>_reset()</t>
-        </is>
-      </c>
     </row>
     <row r="381">
       <c r="A381" s="6" t="n">
@@ -17891,16 +14137,6 @@
         </is>
       </c>
       <c r="H381" s="8" t="n"/>
-      <c r="I381" s="7" t="inlineStr">
-        <is>
-          <t>features/common/theme/theme_screen.dart:1075</t>
-        </is>
-      </c>
-      <c r="J381" s="7" t="inlineStr">
-        <is>
-          <t>_reset()</t>
-        </is>
-      </c>
     </row>
     <row r="382">
       <c r="A382" s="6" t="n">
@@ -17937,16 +14173,6 @@
         </is>
       </c>
       <c r="H382" s="8" t="n"/>
-      <c r="I382" s="7" t="inlineStr">
-        <is>
-          <t>features/common/theme/theme_screen.dart:1271</t>
-        </is>
-      </c>
-      <c r="J382" s="7" t="inlineStr">
-        <is>
-          <t>_reset()</t>
-        </is>
-      </c>
     </row>
     <row r="383">
       <c r="A383" s="6" t="n">
@@ -17983,16 +14209,6 @@
         </is>
       </c>
       <c r="H383" s="8" t="n"/>
-      <c r="I383" s="7" t="inlineStr">
-        <is>
-          <t>features/common/theme/theme_screen.dart:1272</t>
-        </is>
-      </c>
-      <c r="J383" s="7" t="inlineStr">
-        <is>
-          <t>_reset()</t>
-        </is>
-      </c>
     </row>
     <row r="384">
       <c r="A384" s="6" t="n">
@@ -18029,16 +14245,6 @@
         </is>
       </c>
       <c r="H384" s="8" t="n"/>
-      <c r="I384" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/venue_directions_screen.dart:552</t>
-        </is>
-      </c>
-      <c r="J384" s="7" t="inlineStr">
-        <is>
-          <t>_navigate()  if (lat == null || lng == null) &amp;&amp; place.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="385">
       <c r="A385" s="6" t="n">
@@ -18075,16 +14281,6 @@
         </is>
       </c>
       <c r="H385" s="8" t="n"/>
-      <c r="I385" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/venue_directions_screen.dart:562</t>
-        </is>
-      </c>
-      <c r="J385" s="7" t="inlineStr">
-        <is>
-          <t>_navigate()  if !opened &amp;&amp; mounted</t>
-        </is>
-      </c>
     </row>
     <row r="386">
       <c r="A386" s="6" t="n">
@@ -18121,16 +14317,6 @@
         </is>
       </c>
       <c r="H386" s="8" t="n"/>
-      <c r="I386" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_details_screen.dart:55</t>
-        </is>
-      </c>
-      <c r="J386" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="387">
       <c r="A387" s="6" t="n">
@@ -18167,16 +14353,6 @@
         </is>
       </c>
       <c r="H387" s="8" t="n"/>
-      <c r="I387" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_form_screen.dart:164</t>
-        </is>
-      </c>
-      <c r="J387" s="7" t="inlineStr">
-        <is>
-          <t>_pickVideo()  if out == null || !mounted</t>
-        </is>
-      </c>
     </row>
     <row r="388">
       <c r="A388" s="6" t="n">
@@ -18213,16 +14389,6 @@
         </is>
       </c>
       <c r="H388" s="8" t="n"/>
-      <c r="I388" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_form_screen.dart:174</t>
-        </is>
-      </c>
-      <c r="J388" s="7" t="inlineStr">
-        <is>
-          <t>_pickVideo()  if finalSize &gt; _maxVideoBytes</t>
-        </is>
-      </c>
     </row>
     <row r="389">
       <c r="A389" s="6" t="n">
@@ -18259,16 +14425,6 @@
         </is>
       </c>
       <c r="H389" s="8" t="n"/>
-      <c r="I389" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_form_screen.dart:200</t>
-        </is>
-      </c>
-      <c r="J389" s="7" t="inlineStr">
-        <is>
-          <t>_pickVideo()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="390">
       <c r="A390" s="6" t="n">
@@ -18305,16 +14461,6 @@
         </is>
       </c>
       <c r="H390" s="8" t="n"/>
-      <c r="I390" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_form_screen.dart:233</t>
-        </is>
-      </c>
-      <c r="J390" s="7" t="inlineStr">
-        <is>
-          <t>_saveOnce()  if _type == WishPostType.text &amp;&amp; text.isEmpty</t>
-        </is>
-      </c>
     </row>
     <row r="391">
       <c r="A391" s="6" t="n">
@@ -18351,16 +14497,6 @@
         </is>
       </c>
       <c r="H391" s="8" t="n"/>
-      <c r="I391" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_form_screen.dart:240</t>
-        </is>
-      </c>
-      <c r="J391" s="7" t="inlineStr">
-        <is>
-          <t>_saveOnce()  if _type != WishPostType.text &amp;&amp; !_hasMedia</t>
-        </is>
-      </c>
     </row>
     <row r="392">
       <c r="A392" s="6" t="n">
@@ -18397,16 +14533,6 @@
         </is>
       </c>
       <c r="H392" s="8" t="n"/>
-      <c r="I392" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_form_screen.dart:241</t>
-        </is>
-      </c>
-      <c r="J392" s="7" t="inlineStr">
-        <is>
-          <t>_saveOnce()  if _type != WishPostType.text &amp;&amp; !_hasMedia</t>
-        </is>
-      </c>
     </row>
     <row r="393">
       <c r="A393" s="6" t="n">
@@ -18443,16 +14569,6 @@
         </is>
       </c>
       <c r="H393" s="8" t="n"/>
-      <c r="I393" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_form_screen.dart:358</t>
-        </is>
-      </c>
-      <c r="J393" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="394">
       <c r="A394" s="6" t="n">
@@ -18489,16 +14605,6 @@
         </is>
       </c>
       <c r="H394" s="8" t="n"/>
-      <c r="I394" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_message_screen.dart:153</t>
-        </is>
-      </c>
-      <c r="J394" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="395">
       <c r="A395" s="6" t="n">
@@ -18535,16 +14641,6 @@
         </is>
       </c>
       <c r="H395" s="8" t="n"/>
-      <c r="I395" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_widgets.dart:497</t>
-        </is>
-      </c>
-      <c r="J395" s="7" t="inlineStr">
-        <is>
-          <t>point()</t>
-        </is>
-      </c>
     </row>
     <row r="396">
       <c r="A396" s="6" t="n">
@@ -18581,16 +14677,6 @@
         </is>
       </c>
       <c r="H396" s="8" t="n"/>
-      <c r="I396" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wish_widgets.dart:782</t>
-        </is>
-      </c>
-      <c r="J396" s="7" t="inlineStr">
-        <is>
-          <t>open()  if case 'delete'</t>
-        </is>
-      </c>
     </row>
     <row r="397">
       <c r="A397" s="6" t="n">
@@ -18627,16 +14713,6 @@
         </is>
       </c>
       <c r="H397" s="8" t="n"/>
-      <c r="I397" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wishes_screen.dart:153</t>
-        </is>
-      </c>
-      <c r="J397" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="398">
       <c r="A398" s="6" t="n">
@@ -18673,16 +14749,6 @@
         </is>
       </c>
       <c r="H398" s="8" t="n"/>
-      <c r="I398" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wishes_screen.dart:195</t>
-        </is>
-      </c>
-      <c r="J398" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="399">
       <c r="A399" s="6" t="n">
@@ -18719,16 +14785,6 @@
         </is>
       </c>
       <c r="H399" s="8" t="n"/>
-      <c r="I399" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wishes_screen.dart:265</t>
-        </is>
-      </c>
-      <c r="J399" s="7" t="inlineStr">
-        <is>
-          <t>_organizer()</t>
-        </is>
-      </c>
     </row>
     <row r="400">
       <c r="A400" s="6" t="n">
@@ -18765,16 +14821,6 @@
         </is>
       </c>
       <c r="H400" s="8" t="n"/>
-      <c r="I400" s="7" t="inlineStr">
-        <is>
-          <t>features/common/event/wishes/wishes_screen.dart:327</t>
-        </is>
-      </c>
-      <c r="J400" s="7" t="inlineStr">
-        <is>
-          <t>_organizer()  if _tab == WishStatus.blocked</t>
-        </is>
-      </c>
     </row>
     <row r="401">
       <c r="A401" s="6" t="n">
@@ -18811,16 +14857,6 @@
         </is>
       </c>
       <c r="H401" s="8" t="n"/>
-      <c r="I401" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_filter_screen.dart:55</t>
-        </is>
-      </c>
-      <c r="J401" s="7" t="inlineStr">
-        <is>
-          <t>_add()  if _words.any((w) =&gt; w.word.toLowerCase() == key)</t>
-        </is>
-      </c>
     </row>
     <row r="402">
       <c r="A402" s="6" t="n">
@@ -18857,16 +14893,6 @@
         </is>
       </c>
       <c r="H402" s="8" t="n"/>
-      <c r="I402" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_filter_screen.dart:84</t>
-        </is>
-      </c>
-      <c r="J402" s="7" t="inlineStr">
-        <is>
-          <t>_save()  on failure</t>
-        </is>
-      </c>
     </row>
     <row r="403">
       <c r="A403" s="6" t="n">
@@ -18903,16 +14929,6 @@
         </is>
       </c>
       <c r="H403" s="8" t="n"/>
-      <c r="I403" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_filter_screen.dart:145</t>
-        </is>
-      </c>
-      <c r="J403" s="7" t="inlineStr">
-        <is>
-          <t>switchRow()</t>
-        </is>
-      </c>
     </row>
     <row r="404">
       <c r="A404" s="6" t="n">
@@ -18949,16 +14965,6 @@
         </is>
       </c>
       <c r="H404" s="8" t="n"/>
-      <c r="I404" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_filter_screen.dart:175</t>
-        </is>
-      </c>
-      <c r="J404" s="7" t="inlineStr">
-        <is>
-          <t>switchRow()</t>
-        </is>
-      </c>
     </row>
     <row r="405">
       <c r="A405" s="6" t="n">
@@ -18995,16 +15001,6 @@
         </is>
       </c>
       <c r="H405" s="8" t="n"/>
-      <c r="I405" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_filter_screen.dart:206</t>
-        </is>
-      </c>
-      <c r="J405" s="7" t="inlineStr">
-        <is>
-          <t>switchRow()</t>
-        </is>
-      </c>
     </row>
     <row r="406">
       <c r="A406" s="6" t="n">
@@ -19041,16 +15037,6 @@
         </is>
       </c>
       <c r="H406" s="8" t="n"/>
-      <c r="I406" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_filter_screen.dart:329</t>
-        </is>
-      </c>
-      <c r="J406" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="407">
       <c r="A407" s="6" t="n">
@@ -19087,16 +15073,6 @@
         </is>
       </c>
       <c r="H407" s="8" t="n"/>
-      <c r="I407" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_filter_screen.dart:333</t>
-        </is>
-      </c>
-      <c r="J407" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="408">
       <c r="A408" s="6" t="n">
@@ -19133,16 +15109,6 @@
         </is>
       </c>
       <c r="H408" s="8" t="n"/>
-      <c r="I408" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_filter_screen.dart:338</t>
-        </is>
-      </c>
-      <c r="J408" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="409">
       <c r="A409" s="6" t="n">
@@ -19179,16 +15145,6 @@
         </is>
       </c>
       <c r="H409" s="8" t="n"/>
-      <c r="I409" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_settings_screen.dart:122</t>
-        </is>
-      </c>
-      <c r="J409" s="7" t="inlineStr">
-        <is>
-          <t>_save()  if mounted</t>
-        </is>
-      </c>
     </row>
     <row r="410">
       <c r="A410" s="6" t="n">
@@ -19225,16 +15181,6 @@
         </is>
       </c>
       <c r="H410" s="8" t="n"/>
-      <c r="I410" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_settings_screen.dart:161</t>
-        </is>
-      </c>
-      <c r="J410" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" s="6" t="n">
@@ -19271,16 +15217,6 @@
         </is>
       </c>
       <c r="H411" s="8" t="n"/>
-      <c r="I411" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_settings_screen.dart:243</t>
-        </is>
-      </c>
-      <c r="J411" s="7" t="inlineStr">
-        <is>
-          <t>build()  if label == 'Name' &amp;&amp; !v</t>
-        </is>
-      </c>
     </row>
     <row r="412">
       <c r="A412" s="6" t="n">
@@ -19317,22 +15253,12 @@
         </is>
       </c>
       <c r="H412" s="8" t="n"/>
-      <c r="I412" s="7" t="inlineStr">
-        <is>
-          <t>features/organizer/wishes/wish_settings_screen.dart:276</t>
-        </is>
-      </c>
-      <c r="J412" s="7" t="inlineStr">
-        <is>
-          <t>build()</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J412"/>
+  <autoFilter ref="A5:H412"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
